--- a/quiniela_world_cup_mexico_2026.xlsx
+++ b/quiniela_world_cup_mexico_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cfemex-my.sharepoint.com/personal/david_limon_cfe_mx/Documents/RESPALDO DAVID LIMON/iSE/Python y Power BI/Python/quiniela_mundial_mexico_2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="750" documentId="8_{5BF2CA42-94C7-4CF1-99FD-A98BD95C2878}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B7D65F6C-ED81-4751-9328-416A59FD267A}"/>
+  <xr:revisionPtr revIDLastSave="767" documentId="8_{5BF2CA42-94C7-4CF1-99FD-A98BD95C2878}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{79B38FE5-D8E7-4FC7-8BA0-BE581C8D6A69}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FIFA WORLD CUP MEXICO 2026" sheetId="1" r:id="rId1"/>
@@ -842,58 +842,11 @@
       <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -901,6 +854,8 @@
     <xf numFmtId="0" fontId="6" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="14" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -934,6 +889,51 @@
     <xf numFmtId="0" fontId="2" fillId="18" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -963,10 +963,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1257,30 +1253,30 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AK124"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.28515625" customWidth="1"/>
-    <col min="2" max="2" width="8.85546875" customWidth="1"/>
-    <col min="3" max="4" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.33203125" customWidth="1"/>
+    <col min="2" max="2" width="8.88671875" customWidth="1"/>
+    <col min="3" max="4" width="16.6640625" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="4" customWidth="1"/>
-    <col min="7" max="7" width="15.140625" customWidth="1"/>
-    <col min="8" max="9" width="5.7109375" customWidth="1"/>
-    <col min="10" max="10" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="13" width="5.7109375" customWidth="1"/>
-    <col min="14" max="14" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="32" width="5.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.109375" customWidth="1"/>
+    <col min="8" max="9" width="5.6640625" customWidth="1"/>
+    <col min="10" max="10" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.6640625" customWidth="1"/>
+    <col min="14" max="14" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="15" max="32" width="5.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="51" t="s">
+    <row r="1" spans="1:32" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="32" t="s">
         <v>101</v>
       </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="43"/>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="34"/>
       <c r="H1" s="19">
         <v>1</v>
       </c>
@@ -1357,50 +1353,50 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:32" ht="140.44999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="61" t="s">
+    <row r="2" spans="1:32" ht="140.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="46" t="s">
         <v>47</v>
       </c>
-      <c r="B2" s="61"/>
-      <c r="C2" s="62"/>
-      <c r="D2" s="63" t="s">
+      <c r="B2" s="46"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="48" t="s">
         <v>103</v>
       </c>
-      <c r="E2" s="64"/>
-      <c r="F2" s="64"/>
-      <c r="G2" s="65"/>
-      <c r="H2" s="29" t="s">
+      <c r="E2" s="49"/>
+      <c r="F2" s="49"/>
+      <c r="G2" s="50"/>
+      <c r="H2" s="30" t="s">
+        <v>106</v>
+      </c>
+      <c r="I2" s="29" t="s">
+        <v>114</v>
+      </c>
+      <c r="J2" s="30" t="s">
+        <v>107</v>
+      </c>
+      <c r="K2" s="30" t="s">
+        <v>108</v>
+      </c>
+      <c r="L2" s="29" t="s">
+        <v>111</v>
+      </c>
+      <c r="M2" s="29" t="s">
         <v>102</v>
       </c>
-      <c r="I2" s="30" t="s">
+      <c r="N2" s="30" t="s">
+        <v>109</v>
+      </c>
+      <c r="O2" s="29" t="s">
+        <v>115</v>
+      </c>
+      <c r="P2" s="30" t="s">
         <v>105</v>
       </c>
-      <c r="J2" s="30" t="s">
-        <v>106</v>
-      </c>
-      <c r="K2" s="30" t="s">
-        <v>107</v>
-      </c>
-      <c r="L2" s="30" t="s">
-        <v>108</v>
-      </c>
-      <c r="M2" s="30" t="s">
-        <v>109</v>
-      </c>
-      <c r="N2" s="29" t="s">
-        <v>111</v>
-      </c>
-      <c r="O2" s="29" t="s">
+      <c r="Q2" s="29" t="s">
         <v>113</v>
       </c>
-      <c r="P2" s="29" t="s">
+      <c r="R2" s="29" t="s">
         <v>112</v>
-      </c>
-      <c r="Q2" s="29" t="s">
-        <v>115</v>
-      </c>
-      <c r="R2" s="29" t="s">
-        <v>114</v>
       </c>
       <c r="S2" s="29"/>
       <c r="T2" s="29"/>
@@ -1417,7 +1413,7 @@
       <c r="AE2" s="29"/>
       <c r="AF2" s="29"/>
     </row>
-    <row r="3" spans="1:32" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:32" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="14" t="s">
         <v>0</v>
       </c>
@@ -1430,59 +1426,59 @@
       <c r="D3" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="52" t="s">
+      <c r="E3" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="53"/>
+      <c r="F3" s="36"/>
       <c r="G3" s="22" t="s">
         <v>5</v>
       </c>
       <c r="H3" s="14">
-        <f t="shared" ref="H3:AF3" si="0">SUM(IF(H4=$G$4,1,0)+IF(H5=$G$5,1,0)+IF(H6=$G$6,1,0)+IF(H7=$G$7,1,0)+IF(H8=$G$8,1,0)+IF(H9=$G$9,1,0)+IF(H10=$G$10,1,0)+IF(H11=$G$11,1,0)+IF(H12=$G$12,1,0)+IF(H13=$G$13,1,0)+IF(H14=$G$14,1,0)+IF(H15=$G$15,1,0)+IF(H16=$G$16,1,0)+IF(H17=$G$17,1,0)+IF(H18=$G$18,1,0)+IF(H19=$G$19,1,0)+IF(H20=$G$20,1,0)+IF(H21=$G$21,1,0)+IF(H22=$G$22,1,0)+IF(H23=$G$23,1,0)+IF(H24=$G$24,1,0)+IF(H25=$G$25,1,0)+IF(H26=$G$26,1,0)+IF(H27=$G$27,1,0)+IF(H28=$G$28,1,0)+IF(H29=$G$29,1,0)+IF(H30=$G$30,1,0)+IF(H31=$G$31,1,0)+IF(H32=$G$32,1,0)+IF(H33=$G$33,1,0)+IF(H34=$G$34,1,0)+IF(H35=$G$35,1,0)+IF(H36=$G$36,1,0)+IF(H37=$G$37,1,0)+IF(H38=$G$38,1,0)+IF(H39=$G$39,1,0))</f>
-        <v>0</v>
+        <f>SUM(IF(H4=$G$4,1,0)+IF(H5=$G$5,1,0)+IF(H6=$G$6,1,0)+IF(H7=$G$7,1,0)+IF(H8=$G$8,1,0)+IF(H9=$G$9,1,0)+IF(H10=$G$10,1,0)+IF(H11=$G$11,1,0)+IF(H12=$G$12,1,0)+IF(H13=$G$13,1,0)+IF(H14=$G$14,1,0)+IF(H15=$G$15,1,0)+IF(H16=$G$16,1,0)+IF(H17=$G$17,1,0)+IF(H18=$G$18,1,0)+IF(H19=$G$19,1,0)+IF(H20=$G$20,1,0)+IF(H21=$G$21,1,0)+IF(H22=$G$22,1,0)+IF(H23=$G$23,1,0)+IF(H24=$G$24,1,0)+IF(H25=$G$25,1,0)+IF(H26=$G$26,1,0)+IF(H27=$G$27,1,0)+IF(H28=$G$28,1,0)+IF(H29=$G$29,1,0)+IF(H30=$G$30,1,0)+IF(H31=$G$31,1,0)+IF(H32=$G$32,1,0)+IF(H33=$G$33,1,0)+IF(H34=$G$34,1,0)+IF(H35=$G$35,1,0)+IF(H36=$G$36,1,0)+IF(H37=$G$37,1,0)+IF(H38=$G$38,1,0)+IF(H39=$G$39,1,0))</f>
+        <v>6</v>
       </c>
       <c r="I3" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>SUM(IF(I4=$G$4,1,0)+IF(I5=$G$5,1,0)+IF(I6=$G$6,1,0)+IF(I7=$G$7,1,0)+IF(I8=$G$8,1,0)+IF(I9=$G$9,1,0)+IF(I10=$G$10,1,0)+IF(I11=$G$11,1,0)+IF(I12=$G$12,1,0)+IF(I13=$G$13,1,0)+IF(I14=$G$14,1,0)+IF(I15=$G$15,1,0)+IF(I16=$G$16,1,0)+IF(I17=$G$17,1,0)+IF(I18=$G$18,1,0)+IF(I19=$G$19,1,0)+IF(I20=$G$20,1,0)+IF(I21=$G$21,1,0)+IF(I22=$G$22,1,0)+IF(I23=$G$23,1,0)+IF(I24=$G$24,1,0)+IF(I25=$G$25,1,0)+IF(I26=$G$26,1,0)+IF(I27=$G$27,1,0)+IF(I28=$G$28,1,0)+IF(I29=$G$29,1,0)+IF(I30=$G$30,1,0)+IF(I31=$G$31,1,0)+IF(I32=$G$32,1,0)+IF(I33=$G$33,1,0)+IF(I34=$G$34,1,0)+IF(I35=$G$35,1,0)+IF(I36=$G$36,1,0)+IF(I37=$G$37,1,0)+IF(I38=$G$38,1,0)+IF(I39=$G$39,1,0))</f>
+        <v>6</v>
       </c>
       <c r="J3" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>SUM(IF(J4=$G$4,1,0)+IF(J5=$G$5,1,0)+IF(J6=$G$6,1,0)+IF(J7=$G$7,1,0)+IF(J8=$G$8,1,0)+IF(J9=$G$9,1,0)+IF(J10=$G$10,1,0)+IF(J11=$G$11,1,0)+IF(J12=$G$12,1,0)+IF(J13=$G$13,1,0)+IF(J14=$G$14,1,0)+IF(J15=$G$15,1,0)+IF(J16=$G$16,1,0)+IF(J17=$G$17,1,0)+IF(J18=$G$18,1,0)+IF(J19=$G$19,1,0)+IF(J20=$G$20,1,0)+IF(J21=$G$21,1,0)+IF(J22=$G$22,1,0)+IF(J23=$G$23,1,0)+IF(J24=$G$24,1,0)+IF(J25=$G$25,1,0)+IF(J26=$G$26,1,0)+IF(J27=$G$27,1,0)+IF(J28=$G$28,1,0)+IF(J29=$G$29,1,0)+IF(J30=$G$30,1,0)+IF(J31=$G$31,1,0)+IF(J32=$G$32,1,0)+IF(J33=$G$33,1,0)+IF(J34=$G$34,1,0)+IF(J35=$G$35,1,0)+IF(J36=$G$36,1,0)+IF(J37=$G$37,1,0)+IF(J38=$G$38,1,0)+IF(J39=$G$39,1,0))</f>
+        <v>5</v>
       </c>
       <c r="K3" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>SUM(IF(K4=$G$4,1,0)+IF(K5=$G$5,1,0)+IF(K6=$G$6,1,0)+IF(K7=$G$7,1,0)+IF(K8=$G$8,1,0)+IF(K9=$G$9,1,0)+IF(K10=$G$10,1,0)+IF(K11=$G$11,1,0)+IF(K12=$G$12,1,0)+IF(K13=$G$13,1,0)+IF(K14=$G$14,1,0)+IF(K15=$G$15,1,0)+IF(K16=$G$16,1,0)+IF(K17=$G$17,1,0)+IF(K18=$G$18,1,0)+IF(K19=$G$19,1,0)+IF(K20=$G$20,1,0)+IF(K21=$G$21,1,0)+IF(K22=$G$22,1,0)+IF(K23=$G$23,1,0)+IF(K24=$G$24,1,0)+IF(K25=$G$25,1,0)+IF(K26=$G$26,1,0)+IF(K27=$G$27,1,0)+IF(K28=$G$28,1,0)+IF(K29=$G$29,1,0)+IF(K30=$G$30,1,0)+IF(K31=$G$31,1,0)+IF(K32=$G$32,1,0)+IF(K33=$G$33,1,0)+IF(K34=$G$34,1,0)+IF(K35=$G$35,1,0)+IF(K36=$G$36,1,0)+IF(K37=$G$37,1,0)+IF(K38=$G$38,1,0)+IF(K39=$G$39,1,0))</f>
+        <v>5</v>
       </c>
       <c r="L3" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>SUM(IF(L4=$G$4,1,0)+IF(L5=$G$5,1,0)+IF(L6=$G$6,1,0)+IF(L7=$G$7,1,0)+IF(L8=$G$8,1,0)+IF(L9=$G$9,1,0)+IF(L10=$G$10,1,0)+IF(L11=$G$11,1,0)+IF(L12=$G$12,1,0)+IF(L13=$G$13,1,0)+IF(L14=$G$14,1,0)+IF(L15=$G$15,1,0)+IF(L16=$G$16,1,0)+IF(L17=$G$17,1,0)+IF(L18=$G$18,1,0)+IF(L19=$G$19,1,0)+IF(L20=$G$20,1,0)+IF(L21=$G$21,1,0)+IF(L22=$G$22,1,0)+IF(L23=$G$23,1,0)+IF(L24=$G$24,1,0)+IF(L25=$G$25,1,0)+IF(L26=$G$26,1,0)+IF(L27=$G$27,1,0)+IF(L28=$G$28,1,0)+IF(L29=$G$29,1,0)+IF(L30=$G$30,1,0)+IF(L31=$G$31,1,0)+IF(L32=$G$32,1,0)+IF(L33=$G$33,1,0)+IF(L34=$G$34,1,0)+IF(L35=$G$35,1,0)+IF(L36=$G$36,1,0)+IF(L37=$G$37,1,0)+IF(L38=$G$38,1,0)+IF(L39=$G$39,1,0))</f>
+        <v>5</v>
       </c>
       <c r="M3" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>SUM(IF(M4=$G$4,1,0)+IF(M5=$G$5,1,0)+IF(M6=$G$6,1,0)+IF(M7=$G$7,1,0)+IF(M8=$G$8,1,0)+IF(M9=$G$9,1,0)+IF(M10=$G$10,1,0)+IF(M11=$G$11,1,0)+IF(M12=$G$12,1,0)+IF(M13=$G$13,1,0)+IF(M14=$G$14,1,0)+IF(M15=$G$15,1,0)+IF(M16=$G$16,1,0)+IF(M17=$G$17,1,0)+IF(M18=$G$18,1,0)+IF(M19=$G$19,1,0)+IF(M20=$G$20,1,0)+IF(M21=$G$21,1,0)+IF(M22=$G$22,1,0)+IF(M23=$G$23,1,0)+IF(M24=$G$24,1,0)+IF(M25=$G$25,1,0)+IF(M26=$G$26,1,0)+IF(M27=$G$27,1,0)+IF(M28=$G$28,1,0)+IF(M29=$G$29,1,0)+IF(M30=$G$30,1,0)+IF(M31=$G$31,1,0)+IF(M32=$G$32,1,0)+IF(M33=$G$33,1,0)+IF(M34=$G$34,1,0)+IF(M35=$G$35,1,0)+IF(M36=$G$36,1,0)+IF(M37=$G$37,1,0)+IF(M38=$G$38,1,0)+IF(M39=$G$39,1,0))</f>
+        <v>4</v>
       </c>
       <c r="N3" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>SUM(IF(N4=$G$4,1,0)+IF(N5=$G$5,1,0)+IF(N6=$G$6,1,0)+IF(N7=$G$7,1,0)+IF(N8=$G$8,1,0)+IF(N9=$G$9,1,0)+IF(N10=$G$10,1,0)+IF(N11=$G$11,1,0)+IF(N12=$G$12,1,0)+IF(N13=$G$13,1,0)+IF(N14=$G$14,1,0)+IF(N15=$G$15,1,0)+IF(N16=$G$16,1,0)+IF(N17=$G$17,1,0)+IF(N18=$G$18,1,0)+IF(N19=$G$19,1,0)+IF(N20=$G$20,1,0)+IF(N21=$G$21,1,0)+IF(N22=$G$22,1,0)+IF(N23=$G$23,1,0)+IF(N24=$G$24,1,0)+IF(N25=$G$25,1,0)+IF(N26=$G$26,1,0)+IF(N27=$G$27,1,0)+IF(N28=$G$28,1,0)+IF(N29=$G$29,1,0)+IF(N30=$G$30,1,0)+IF(N31=$G$31,1,0)+IF(N32=$G$32,1,0)+IF(N33=$G$33,1,0)+IF(N34=$G$34,1,0)+IF(N35=$G$35,1,0)+IF(N36=$G$36,1,0)+IF(N37=$G$37,1,0)+IF(N38=$G$38,1,0)+IF(N39=$G$39,1,0))</f>
+        <v>4</v>
       </c>
       <c r="O3" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>SUM(IF(O4=$G$4,1,0)+IF(O5=$G$5,1,0)+IF(O6=$G$6,1,0)+IF(O7=$G$7,1,0)+IF(O8=$G$8,1,0)+IF(O9=$G$9,1,0)+IF(O10=$G$10,1,0)+IF(O11=$G$11,1,0)+IF(O12=$G$12,1,0)+IF(O13=$G$13,1,0)+IF(O14=$G$14,1,0)+IF(O15=$G$15,1,0)+IF(O16=$G$16,1,0)+IF(O17=$G$17,1,0)+IF(O18=$G$18,1,0)+IF(O19=$G$19,1,0)+IF(O20=$G$20,1,0)+IF(O21=$G$21,1,0)+IF(O22=$G$22,1,0)+IF(O23=$G$23,1,0)+IF(O24=$G$24,1,0)+IF(O25=$G$25,1,0)+IF(O26=$G$26,1,0)+IF(O27=$G$27,1,0)+IF(O28=$G$28,1,0)+IF(O29=$G$29,1,0)+IF(O30=$G$30,1,0)+IF(O31=$G$31,1,0)+IF(O32=$G$32,1,0)+IF(O33=$G$33,1,0)+IF(O34=$G$34,1,0)+IF(O35=$G$35,1,0)+IF(O36=$G$36,1,0)+IF(O37=$G$37,1,0)+IF(O38=$G$38,1,0)+IF(O39=$G$39,1,0))</f>
+        <v>4</v>
       </c>
       <c r="P3" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>SUM(IF(P4=$G$4,1,0)+IF(P5=$G$5,1,0)+IF(P6=$G$6,1,0)+IF(P7=$G$7,1,0)+IF(P8=$G$8,1,0)+IF(P9=$G$9,1,0)+IF(P10=$G$10,1,0)+IF(P11=$G$11,1,0)+IF(P12=$G$12,1,0)+IF(P13=$G$13,1,0)+IF(P14=$G$14,1,0)+IF(P15=$G$15,1,0)+IF(P16=$G$16,1,0)+IF(P17=$G$17,1,0)+IF(P18=$G$18,1,0)+IF(P19=$G$19,1,0)+IF(P20=$G$20,1,0)+IF(P21=$G$21,1,0)+IF(P22=$G$22,1,0)+IF(P23=$G$23,1,0)+IF(P24=$G$24,1,0)+IF(P25=$G$25,1,0)+IF(P26=$G$26,1,0)+IF(P27=$G$27,1,0)+IF(P28=$G$28,1,0)+IF(P29=$G$29,1,0)+IF(P30=$G$30,1,0)+IF(P31=$G$31,1,0)+IF(P32=$G$32,1,0)+IF(P33=$G$33,1,0)+IF(P34=$G$34,1,0)+IF(P35=$G$35,1,0)+IF(P36=$G$36,1,0)+IF(P37=$G$37,1,0)+IF(P38=$G$38,1,0)+IF(P39=$G$39,1,0))</f>
+        <v>3</v>
       </c>
       <c r="Q3" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>SUM(IF(Q4=$G$4,1,0)+IF(Q5=$G$5,1,0)+IF(Q6=$G$6,1,0)+IF(Q7=$G$7,1,0)+IF(Q8=$G$8,1,0)+IF(Q9=$G$9,1,0)+IF(Q10=$G$10,1,0)+IF(Q11=$G$11,1,0)+IF(Q12=$G$12,1,0)+IF(Q13=$G$13,1,0)+IF(Q14=$G$14,1,0)+IF(Q15=$G$15,1,0)+IF(Q16=$G$16,1,0)+IF(Q17=$G$17,1,0)+IF(Q18=$G$18,1,0)+IF(Q19=$G$19,1,0)+IF(Q20=$G$20,1,0)+IF(Q21=$G$21,1,0)+IF(Q22=$G$22,1,0)+IF(Q23=$G$23,1,0)+IF(Q24=$G$24,1,0)+IF(Q25=$G$25,1,0)+IF(Q26=$G$26,1,0)+IF(Q27=$G$27,1,0)+IF(Q28=$G$28,1,0)+IF(Q29=$G$29,1,0)+IF(Q30=$G$30,1,0)+IF(Q31=$G$31,1,0)+IF(Q32=$G$32,1,0)+IF(Q33=$G$33,1,0)+IF(Q34=$G$34,1,0)+IF(Q35=$G$35,1,0)+IF(Q36=$G$36,1,0)+IF(Q37=$G$37,1,0)+IF(Q38=$G$38,1,0)+IF(Q39=$G$39,1,0))</f>
+        <v>3</v>
       </c>
       <c r="R3" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>SUM(IF(R4=$G$4,1,0)+IF(R5=$G$5,1,0)+IF(R6=$G$6,1,0)+IF(R7=$G$7,1,0)+IF(R8=$G$8,1,0)+IF(R9=$G$9,1,0)+IF(R10=$G$10,1,0)+IF(R11=$G$11,1,0)+IF(R12=$G$12,1,0)+IF(R13=$G$13,1,0)+IF(R14=$G$14,1,0)+IF(R15=$G$15,1,0)+IF(R16=$G$16,1,0)+IF(R17=$G$17,1,0)+IF(R18=$G$18,1,0)+IF(R19=$G$19,1,0)+IF(R20=$G$20,1,0)+IF(R21=$G$21,1,0)+IF(R22=$G$22,1,0)+IF(R23=$G$23,1,0)+IF(R24=$G$24,1,0)+IF(R25=$G$25,1,0)+IF(R26=$G$26,1,0)+IF(R27=$G$27,1,0)+IF(R28=$G$28,1,0)+IF(R29=$G$29,1,0)+IF(R30=$G$30,1,0)+IF(R31=$G$31,1,0)+IF(R32=$G$32,1,0)+IF(R33=$G$33,1,0)+IF(R34=$G$34,1,0)+IF(R35=$G$35,1,0)+IF(R36=$G$36,1,0)+IF(R37=$G$37,1,0)+IF(R38=$G$38,1,0)+IF(R39=$G$39,1,0))</f>
+        <v>3</v>
       </c>
       <c r="S3" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="H3:AF3" si="0">SUM(IF(S4=$G$4,1,0)+IF(S5=$G$5,1,0)+IF(S6=$G$6,1,0)+IF(S7=$G$7,1,0)+IF(S8=$G$8,1,0)+IF(S9=$G$9,1,0)+IF(S10=$G$10,1,0)+IF(S11=$G$11,1,0)+IF(S12=$G$12,1,0)+IF(S13=$G$13,1,0)+IF(S14=$G$14,1,0)+IF(S15=$G$15,1,0)+IF(S16=$G$16,1,0)+IF(S17=$G$17,1,0)+IF(S18=$G$18,1,0)+IF(S19=$G$19,1,0)+IF(S20=$G$20,1,0)+IF(S21=$G$21,1,0)+IF(S22=$G$22,1,0)+IF(S23=$G$23,1,0)+IF(S24=$G$24,1,0)+IF(S25=$G$25,1,0)+IF(S26=$G$26,1,0)+IF(S27=$G$27,1,0)+IF(S28=$G$28,1,0)+IF(S29=$G$29,1,0)+IF(S30=$G$30,1,0)+IF(S31=$G$31,1,0)+IF(S32=$G$32,1,0)+IF(S33=$G$33,1,0)+IF(S34=$G$34,1,0)+IF(S35=$G$35,1,0)+IF(S36=$G$36,1,0)+IF(S37=$G$37,1,0)+IF(S38=$G$38,1,0)+IF(S39=$G$39,1,0))</f>
         <v>0</v>
       </c>
       <c r="T3" s="14">
@@ -1538,8 +1534,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="54" t="s">
+    <row r="4" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="37" t="s">
         <v>6</v>
       </c>
       <c r="B4" s="7">
@@ -1551,16 +1547,20 @@
       <c r="D4" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
+      <c r="E4" s="7">
+        <v>2</v>
+      </c>
+      <c r="F4" s="7">
+        <v>0</v>
+      </c>
       <c r="G4" s="7" t="str">
         <f t="shared" ref="G4:G51" si="1">IF(E4="","-",IF(E4&gt;F4,"L",IF(E4=F4,"E",IF(E4&lt;F4,"V"))))</f>
-        <v>-</v>
-      </c>
-      <c r="H4" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="I4" s="24" t="s">
+        <v>L</v>
+      </c>
+      <c r="H4" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="I4" s="23" t="s">
         <v>46</v>
       </c>
       <c r="J4" s="24" t="s">
@@ -1569,19 +1569,19 @@
       <c r="K4" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="L4" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="M4" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="N4" s="23" t="s">
+      <c r="L4" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="M4" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="N4" s="24" t="s">
         <v>46</v>
       </c>
       <c r="O4" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="P4" s="23" t="s">
+      <c r="P4" s="24" t="s">
         <v>46</v>
       </c>
       <c r="Q4" s="23" t="s">
@@ -1605,8 +1605,8 @@
       <c r="AE4" s="23"/>
       <c r="AF4" s="23"/>
     </row>
-    <row r="5" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="39"/>
+    <row r="5" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="38"/>
       <c r="B5" s="7">
         <v>2</v>
       </c>
@@ -1616,17 +1616,21 @@
       <c r="D5" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
+      <c r="E5" s="7">
+        <v>2</v>
+      </c>
+      <c r="F5" s="7">
+        <v>1</v>
+      </c>
       <c r="G5" s="7" t="str">
         <f t="shared" si="1"/>
-        <v>-</v>
-      </c>
-      <c r="H5" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="I5" s="24" t="s">
-        <v>10</v>
+        <v>L</v>
+      </c>
+      <c r="H5" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="I5" s="23" t="s">
+        <v>46</v>
       </c>
       <c r="J5" s="24" t="s">
         <v>46</v>
@@ -1634,26 +1638,26 @@
       <c r="K5" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="L5" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="M5" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="N5" s="23" t="s">
+      <c r="L5" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="M5" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="N5" s="24" t="s">
         <v>46</v>
       </c>
       <c r="O5" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="P5" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="P5" s="24" t="s">
         <v>10</v>
       </c>
       <c r="Q5" s="23" t="s">
-        <v>104</v>
+        <v>10</v>
       </c>
       <c r="R5" s="23" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="S5" s="23"/>
       <c r="T5" s="23"/>
@@ -1670,8 +1674,8 @@
       <c r="AE5" s="23"/>
       <c r="AF5" s="23"/>
     </row>
-    <row r="6" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="39"/>
+    <row r="6" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="38"/>
       <c r="B6" s="7">
         <v>3</v>
       </c>
@@ -1687,31 +1691,31 @@
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
-      <c r="H6" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="I6" s="24" t="s">
+      <c r="H6" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="I6" s="23" t="s">
         <v>46</v>
       </c>
       <c r="J6" s="24" t="s">
-        <v>46</v>
+        <v>110</v>
       </c>
       <c r="K6" s="24" t="s">
-        <v>110</v>
-      </c>
-      <c r="L6" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="M6" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="N6" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="L6" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="M6" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="N6" s="24" t="s">
         <v>10</v>
       </c>
       <c r="O6" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="P6" s="23" t="s">
+      <c r="P6" s="24" t="s">
         <v>46</v>
       </c>
       <c r="Q6" s="23" t="s">
@@ -1735,8 +1739,8 @@
       <c r="AE6" s="23"/>
       <c r="AF6" s="23"/>
     </row>
-    <row r="7" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="39"/>
+    <row r="7" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="38"/>
       <c r="B7" s="7">
         <v>4</v>
       </c>
@@ -1752,38 +1756,38 @@
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
-      <c r="H7" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="I7" s="24" t="s">
-        <v>104</v>
+      <c r="H7" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="I7" s="23" t="s">
+        <v>10</v>
       </c>
       <c r="J7" s="24" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="K7" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="L7" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="M7" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="N7" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="L7" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="M7" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="N7" s="24" t="s">
         <v>46</v>
       </c>
       <c r="O7" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="P7" s="23" t="s">
-        <v>46</v>
+      <c r="P7" s="24" t="s">
+        <v>104</v>
       </c>
       <c r="Q7" s="23" t="s">
         <v>46</v>
       </c>
       <c r="R7" s="23" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="S7" s="23"/>
       <c r="T7" s="23"/>
@@ -1800,8 +1804,8 @@
       <c r="AE7" s="23"/>
       <c r="AF7" s="23"/>
     </row>
-    <row r="8" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="39"/>
+    <row r="8" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="38"/>
       <c r="B8" s="7">
         <v>5</v>
       </c>
@@ -1817,11 +1821,11 @@
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
-      <c r="H8" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="I8" s="24" t="s">
-        <v>104</v>
+      <c r="H8" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="I8" s="23" t="s">
+        <v>46</v>
       </c>
       <c r="J8" s="24" t="s">
         <v>104</v>
@@ -1829,26 +1833,26 @@
       <c r="K8" s="24" t="s">
         <v>104</v>
       </c>
-      <c r="L8" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="M8" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="N8" s="23" t="s">
-        <v>104</v>
+      <c r="L8" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="M8" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="N8" s="24" t="s">
+        <v>10</v>
       </c>
       <c r="O8" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="P8" s="23" t="s">
+      <c r="P8" s="24" t="s">
         <v>104</v>
       </c>
       <c r="Q8" s="23" t="s">
         <v>104</v>
       </c>
       <c r="R8" s="23" t="s">
-        <v>46</v>
+        <v>104</v>
       </c>
       <c r="S8" s="23"/>
       <c r="T8" s="23"/>
@@ -1865,8 +1869,8 @@
       <c r="AE8" s="23"/>
       <c r="AF8" s="23"/>
     </row>
-    <row r="9" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="40"/>
+    <row r="9" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="39"/>
       <c r="B9" s="7">
         <v>6</v>
       </c>
@@ -1882,35 +1886,35 @@
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
-      <c r="H9" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="I9" s="24" t="s">
-        <v>104</v>
+      <c r="H9" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="I9" s="23" t="s">
+        <v>10</v>
       </c>
       <c r="J9" s="24" t="s">
-        <v>46</v>
+        <v>104</v>
       </c>
       <c r="K9" s="24" t="s">
         <v>104</v>
       </c>
-      <c r="L9" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="M9" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="N9" s="23" t="s">
+      <c r="L9" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="M9" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="N9" s="24" t="s">
         <v>104</v>
       </c>
       <c r="O9" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="P9" s="23" t="s">
-        <v>10</v>
+        <v>10</v>
+      </c>
+      <c r="P9" s="24" t="s">
+        <v>104</v>
       </c>
       <c r="Q9" s="23" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="R9" s="23" t="s">
         <v>10</v>
@@ -1930,8 +1934,8 @@
       <c r="AE9" s="23"/>
       <c r="AF9" s="23"/>
     </row>
-    <row r="10" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A10" s="59" t="s">
+    <row r="10" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="44" t="s">
         <v>7</v>
       </c>
       <c r="B10" s="7">
@@ -1943,38 +1947,42 @@
       <c r="D10" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
+      <c r="E10" s="8">
+        <v>1</v>
+      </c>
+      <c r="F10" s="8">
+        <v>1</v>
+      </c>
       <c r="G10" s="8" t="str">
         <f t="shared" si="1"/>
-        <v>-</v>
-      </c>
-      <c r="H10" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="I10" s="24" t="s">
-        <v>46</v>
+        <v>E</v>
+      </c>
+      <c r="H10" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="I10" s="23" t="s">
+        <v>10</v>
       </c>
       <c r="J10" s="24" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="K10" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="L10" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="M10" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="N10" s="23" t="s">
+      <c r="L10" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="M10" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="N10" s="24" t="s">
         <v>10</v>
       </c>
       <c r="O10" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="P10" s="23" t="s">
-        <v>10</v>
+      <c r="P10" s="24" t="s">
+        <v>46</v>
       </c>
       <c r="Q10" s="23" t="s">
         <v>46</v>
@@ -1997,8 +2005,8 @@
       <c r="AE10" s="23"/>
       <c r="AF10" s="23"/>
     </row>
-    <row r="11" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A11" s="39"/>
+    <row r="11" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A11" s="38"/>
       <c r="B11" s="7">
         <v>8</v>
       </c>
@@ -2008,44 +2016,48 @@
       <c r="D11" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
+      <c r="E11" s="8">
+        <v>1</v>
+      </c>
+      <c r="F11" s="8">
+        <v>1</v>
+      </c>
       <c r="G11" s="8" t="str">
         <f t="shared" si="1"/>
-        <v>-</v>
-      </c>
-      <c r="H11" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="I11" s="24" t="s">
-        <v>104</v>
+        <v>E</v>
+      </c>
+      <c r="H11" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="I11" s="23" t="s">
+        <v>10</v>
       </c>
       <c r="J11" s="24" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="K11" s="24" t="s">
         <v>104</v>
       </c>
-      <c r="L11" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="M11" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="N11" s="23" t="s">
-        <v>104</v>
+      <c r="L11" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="M11" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="N11" s="24" t="s">
+        <v>46</v>
       </c>
       <c r="O11" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="P11" s="23" t="s">
+      <c r="P11" s="24" t="s">
         <v>104</v>
       </c>
       <c r="Q11" s="23" t="s">
         <v>104</v>
       </c>
       <c r="R11" s="23" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="S11" s="23"/>
       <c r="T11" s="23"/>
@@ -2062,8 +2074,8 @@
       <c r="AE11" s="23"/>
       <c r="AF11" s="23"/>
     </row>
-    <row r="12" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A12" s="39"/>
+    <row r="12" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A12" s="38"/>
       <c r="B12" s="7">
         <v>9</v>
       </c>
@@ -2079,38 +2091,38 @@
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
-      <c r="H12" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="I12" s="24" t="s">
-        <v>10</v>
+      <c r="H12" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="I12" s="23" t="s">
+        <v>46</v>
       </c>
       <c r="J12" s="24" t="s">
         <v>46</v>
       </c>
       <c r="K12" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="L12" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="M12" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="N12" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="L12" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="M12" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="N12" s="24" t="s">
         <v>46</v>
       </c>
       <c r="O12" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="P12" s="23" t="s">
-        <v>104</v>
+      <c r="P12" s="24" t="s">
+        <v>10</v>
       </c>
       <c r="Q12" s="23" t="s">
         <v>46</v>
       </c>
       <c r="R12" s="23" t="s">
-        <v>46</v>
+        <v>104</v>
       </c>
       <c r="S12" s="23"/>
       <c r="T12" s="23"/>
@@ -2127,8 +2139,8 @@
       <c r="AE12" s="23"/>
       <c r="AF12" s="23"/>
     </row>
-    <row r="13" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A13" s="39"/>
+    <row r="13" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A13" s="38"/>
       <c r="B13" s="7">
         <v>10</v>
       </c>
@@ -2144,31 +2156,31 @@
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
-      <c r="H13" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="I13" s="24" t="s">
+      <c r="H13" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="I13" s="23" t="s">
         <v>46</v>
       </c>
       <c r="J13" s="24" t="s">
         <v>46</v>
       </c>
       <c r="K13" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="L13" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="M13" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="N13" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="L13" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="M13" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="N13" s="24" t="s">
         <v>46</v>
       </c>
       <c r="O13" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="P13" s="23" t="s">
+      <c r="P13" s="24" t="s">
         <v>46</v>
       </c>
       <c r="Q13" s="23" t="s">
@@ -2192,8 +2204,8 @@
       <c r="AE13" s="23"/>
       <c r="AF13" s="23"/>
     </row>
-    <row r="14" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="39"/>
+    <row r="14" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A14" s="38"/>
       <c r="B14" s="7">
         <v>11</v>
       </c>
@@ -2209,10 +2221,10 @@
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
-      <c r="H14" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="I14" s="24" t="s">
+      <c r="H14" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="I14" s="23" t="s">
         <v>104</v>
       </c>
       <c r="J14" s="24" t="s">
@@ -2221,19 +2233,19 @@
       <c r="K14" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="L14" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="M14" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="N14" s="23" t="s">
-        <v>46</v>
+      <c r="L14" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="M14" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="N14" s="24" t="s">
+        <v>104</v>
       </c>
       <c r="O14" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="P14" s="23" t="s">
+      <c r="P14" s="24" t="s">
         <v>104</v>
       </c>
       <c r="Q14" s="23" t="s">
@@ -2257,8 +2269,8 @@
       <c r="AE14" s="23"/>
       <c r="AF14" s="23"/>
     </row>
-    <row r="15" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A15" s="40"/>
+    <row r="15" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A15" s="39"/>
       <c r="B15" s="7">
         <v>12</v>
       </c>
@@ -2274,35 +2286,35 @@
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
-      <c r="H15" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="I15" s="24" t="s">
-        <v>46</v>
+      <c r="H15" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="I15" s="23" t="s">
+        <v>104</v>
       </c>
       <c r="J15" s="24" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="K15" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="L15" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="M15" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="N15" s="23" t="s">
-        <v>10</v>
+        <v>104</v>
+      </c>
+      <c r="L15" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="M15" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="N15" s="24" t="s">
+        <v>46</v>
       </c>
       <c r="O15" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="P15" s="23" t="s">
-        <v>104</v>
+        <v>10</v>
+      </c>
+      <c r="P15" s="24" t="s">
+        <v>46</v>
       </c>
       <c r="Q15" s="23" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="R15" s="23" t="s">
         <v>104</v>
@@ -2322,8 +2334,8 @@
       <c r="AE15" s="23"/>
       <c r="AF15" s="23"/>
     </row>
-    <row r="16" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A16" s="60" t="s">
+    <row r="16" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A16" s="45" t="s">
         <v>8</v>
       </c>
       <c r="B16" s="7">
@@ -2335,17 +2347,21 @@
       <c r="D16" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
+      <c r="E16" s="9">
+        <v>1</v>
+      </c>
+      <c r="F16" s="9">
+        <v>1</v>
+      </c>
       <c r="G16" s="9" t="str">
         <f t="shared" si="1"/>
-        <v>-</v>
-      </c>
-      <c r="H16" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="I16" s="24" t="s">
-        <v>104</v>
+        <v>E</v>
+      </c>
+      <c r="H16" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="I16" s="23" t="s">
+        <v>46</v>
       </c>
       <c r="J16" s="24" t="s">
         <v>46</v>
@@ -2353,20 +2369,20 @@
       <c r="K16" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="L16" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="M16" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="N16" s="23" t="s">
-        <v>10</v>
+      <c r="L16" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="M16" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="N16" s="24" t="s">
+        <v>46</v>
       </c>
       <c r="O16" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="P16" s="23" t="s">
-        <v>46</v>
+      <c r="P16" s="24" t="s">
+        <v>104</v>
       </c>
       <c r="Q16" s="23" t="s">
         <v>46</v>
@@ -2389,8 +2405,8 @@
       <c r="AE16" s="23"/>
       <c r="AF16" s="23"/>
     </row>
-    <row r="17" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A17" s="39"/>
+    <row r="17" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A17" s="38"/>
       <c r="B17" s="7">
         <v>14</v>
       </c>
@@ -2400,16 +2416,20 @@
       <c r="D17" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
+      <c r="E17" s="9">
+        <v>0</v>
+      </c>
+      <c r="F17" s="9">
+        <v>1</v>
+      </c>
       <c r="G17" s="9" t="str">
         <f t="shared" si="1"/>
-        <v>-</v>
-      </c>
-      <c r="H17" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="I17" s="24" t="s">
+        <v>V</v>
+      </c>
+      <c r="H17" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="I17" s="23" t="s">
         <v>104</v>
       </c>
       <c r="J17" s="24" t="s">
@@ -2418,19 +2438,19 @@
       <c r="K17" s="24" t="s">
         <v>104</v>
       </c>
-      <c r="L17" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="M17" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="N17" s="23" t="s">
+      <c r="L17" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="M17" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="N17" s="24" t="s">
         <v>104</v>
       </c>
       <c r="O17" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="P17" s="23" t="s">
+      <c r="P17" s="24" t="s">
         <v>104</v>
       </c>
       <c r="Q17" s="23" t="s">
@@ -2454,8 +2474,8 @@
       <c r="AE17" s="23"/>
       <c r="AF17" s="23"/>
     </row>
-    <row r="18" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A18" s="39"/>
+    <row r="18" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A18" s="38"/>
       <c r="B18" s="7">
         <v>15</v>
       </c>
@@ -2471,35 +2491,35 @@
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
-      <c r="H18" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="I18" s="24" t="s">
+      <c r="H18" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="I18" s="23" t="s">
         <v>104</v>
       </c>
       <c r="J18" s="24" t="s">
-        <v>104</v>
+        <v>46</v>
       </c>
       <c r="K18" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="L18" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="M18" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="N18" s="23" t="s">
-        <v>104</v>
+        <v>10</v>
+      </c>
+      <c r="L18" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="M18" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="N18" s="24" t="s">
+        <v>46</v>
       </c>
       <c r="O18" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="P18" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="P18" s="24" t="s">
         <v>104</v>
       </c>
       <c r="Q18" s="23" t="s">
-        <v>46</v>
+        <v>104</v>
       </c>
       <c r="R18" s="23" t="s">
         <v>104</v>
@@ -2519,8 +2539,8 @@
       <c r="AE18" s="23"/>
       <c r="AF18" s="23"/>
     </row>
-    <row r="19" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A19" s="39"/>
+    <row r="19" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A19" s="38"/>
       <c r="B19" s="7">
         <v>16</v>
       </c>
@@ -2536,10 +2556,10 @@
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
-      <c r="H19" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="I19" s="24" t="s">
+      <c r="H19" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="I19" s="23" t="s">
         <v>46</v>
       </c>
       <c r="J19" s="24" t="s">
@@ -2548,19 +2568,19 @@
       <c r="K19" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="L19" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="M19" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="N19" s="23" t="s">
+      <c r="L19" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="M19" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="N19" s="24" t="s">
         <v>46</v>
       </c>
       <c r="O19" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="P19" s="23" t="s">
+      <c r="P19" s="24" t="s">
         <v>46</v>
       </c>
       <c r="Q19" s="23" t="s">
@@ -2584,8 +2604,8 @@
       <c r="AE19" s="23"/>
       <c r="AF19" s="23"/>
     </row>
-    <row r="20" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A20" s="39"/>
+    <row r="20" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A20" s="38"/>
       <c r="B20" s="7">
         <v>17</v>
       </c>
@@ -2601,31 +2621,31 @@
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
-      <c r="H20" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="I20" s="24" t="s">
+      <c r="H20" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="I20" s="23" t="s">
         <v>104</v>
       </c>
       <c r="J20" s="24" t="s">
-        <v>104</v>
+        <v>46</v>
       </c>
       <c r="K20" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="L20" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="M20" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="N20" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="L20" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="M20" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="N20" s="24" t="s">
         <v>104</v>
       </c>
       <c r="O20" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="P20" s="23" t="s">
+      <c r="P20" s="24" t="s">
         <v>104</v>
       </c>
       <c r="Q20" s="23" t="s">
@@ -2649,8 +2669,8 @@
       <c r="AE20" s="23"/>
       <c r="AF20" s="23"/>
     </row>
-    <row r="21" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A21" s="40"/>
+    <row r="21" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A21" s="39"/>
       <c r="B21" s="7">
         <v>18</v>
       </c>
@@ -2666,10 +2686,10 @@
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
-      <c r="H21" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="I21" s="24" t="s">
+      <c r="H21" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="I21" s="23" t="s">
         <v>46</v>
       </c>
       <c r="J21" s="24" t="s">
@@ -2678,23 +2698,23 @@
       <c r="K21" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="L21" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="M21" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="N21" s="23" t="s">
+      <c r="L21" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="M21" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="N21" s="24" t="s">
         <v>46</v>
       </c>
       <c r="O21" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="P21" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="P21" s="24" t="s">
         <v>46</v>
       </c>
       <c r="Q21" s="23" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="R21" s="23" t="s">
         <v>46</v>
@@ -2714,8 +2734,8 @@
       <c r="AE21" s="23"/>
       <c r="AF21" s="23"/>
     </row>
-    <row r="22" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A22" s="57" t="s">
+    <row r="22" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A22" s="42" t="s">
         <v>9</v>
       </c>
       <c r="B22" s="7">
@@ -2727,17 +2747,21 @@
       <c r="D22" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="E22" s="10"/>
-      <c r="F22" s="10"/>
+      <c r="E22" s="10">
+        <v>4</v>
+      </c>
+      <c r="F22" s="10">
+        <v>1</v>
+      </c>
       <c r="G22" s="10" t="str">
         <f t="shared" si="1"/>
-        <v>-</v>
-      </c>
-      <c r="H22" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="I22" s="24" t="s">
-        <v>46</v>
+        <v>L</v>
+      </c>
+      <c r="H22" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="I22" s="23" t="s">
+        <v>104</v>
       </c>
       <c r="J22" s="24" t="s">
         <v>46</v>
@@ -2745,26 +2769,26 @@
       <c r="K22" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="L22" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="M22" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="N22" s="23" t="s">
-        <v>10</v>
+      <c r="L22" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="M22" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="N22" s="24" t="s">
+        <v>104</v>
       </c>
       <c r="O22" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="P22" s="23" t="s">
-        <v>10</v>
+      <c r="P22" s="24" t="s">
+        <v>46</v>
       </c>
       <c r="Q22" s="23" t="s">
         <v>46</v>
       </c>
       <c r="R22" s="23" t="s">
-        <v>104</v>
+        <v>10</v>
       </c>
       <c r="S22" s="23"/>
       <c r="T22" s="23"/>
@@ -2781,8 +2805,8 @@
       <c r="AE22" s="23"/>
       <c r="AF22" s="23"/>
     </row>
-    <row r="23" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A23" s="39"/>
+    <row r="23" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A23" s="38"/>
       <c r="B23" s="7">
         <v>20</v>
       </c>
@@ -2792,44 +2816,48 @@
       <c r="D23" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="E23" s="10"/>
-      <c r="F23" s="10"/>
+      <c r="E23" s="10">
+        <v>2</v>
+      </c>
+      <c r="F23" s="10">
+        <v>0</v>
+      </c>
       <c r="G23" s="10" t="str">
         <f t="shared" si="1"/>
-        <v>-</v>
-      </c>
-      <c r="H23" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="I23" s="24" t="s">
-        <v>104</v>
+        <v>L</v>
+      </c>
+      <c r="H23" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="I23" s="23" t="s">
+        <v>46</v>
       </c>
       <c r="J23" s="24" t="s">
-        <v>104</v>
+        <v>46</v>
       </c>
       <c r="K23" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="L23" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="M23" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="N23" s="23" t="s">
+      <c r="L23" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="M23" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="N23" s="24" t="s">
         <v>10</v>
       </c>
       <c r="O23" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="P23" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="P23" s="24" t="s">
         <v>104</v>
       </c>
       <c r="Q23" s="23" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="R23" s="23" t="s">
-        <v>46</v>
+        <v>104</v>
       </c>
       <c r="S23" s="23"/>
       <c r="T23" s="23"/>
@@ -2846,8 +2874,8 @@
       <c r="AE23" s="23"/>
       <c r="AF23" s="23"/>
     </row>
-    <row r="24" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A24" s="39"/>
+    <row r="24" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A24" s="38"/>
       <c r="B24" s="7">
         <v>21</v>
       </c>
@@ -2863,32 +2891,32 @@
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
-      <c r="H24" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="I24" s="24" t="s">
-        <v>10</v>
+      <c r="H24" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="I24" s="23" t="s">
+        <v>46</v>
       </c>
       <c r="J24" s="24" t="s">
         <v>46</v>
       </c>
       <c r="K24" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="L24" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="M24" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="N24" s="23" t="s">
-        <v>104</v>
+        <v>10</v>
+      </c>
+      <c r="L24" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="M24" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="N24" s="24" t="s">
+        <v>46</v>
       </c>
       <c r="O24" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="P24" s="23" t="s">
-        <v>46</v>
+      <c r="P24" s="24" t="s">
+        <v>10</v>
       </c>
       <c r="Q24" s="23" t="s">
         <v>46</v>
@@ -2911,8 +2939,8 @@
       <c r="AE24" s="23"/>
       <c r="AF24" s="23"/>
     </row>
-    <row r="25" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A25" s="39"/>
+    <row r="25" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A25" s="38"/>
       <c r="B25" s="7">
         <v>22</v>
       </c>
@@ -2928,32 +2956,32 @@
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
-      <c r="H25" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="I25" s="24" t="s">
-        <v>46</v>
+      <c r="H25" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="I25" s="23" t="s">
+        <v>10</v>
       </c>
       <c r="J25" s="24" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="K25" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="L25" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="M25" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="N25" s="23" t="s">
-        <v>46</v>
+        <v>104</v>
+      </c>
+      <c r="L25" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="M25" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="N25" s="24" t="s">
+        <v>104</v>
       </c>
       <c r="O25" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="P25" s="23" t="s">
-        <v>10</v>
+      <c r="P25" s="24" t="s">
+        <v>46</v>
       </c>
       <c r="Q25" s="23" t="s">
         <v>10</v>
@@ -2976,8 +3004,8 @@
       <c r="AE25" s="23"/>
       <c r="AF25" s="23"/>
     </row>
-    <row r="26" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A26" s="39"/>
+    <row r="26" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A26" s="38"/>
       <c r="B26" s="7">
         <v>23</v>
       </c>
@@ -2993,38 +3021,38 @@
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
-      <c r="H26" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="I26" s="24" t="s">
+      <c r="H26" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="I26" s="23" t="s">
         <v>10</v>
       </c>
       <c r="J26" s="24" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="K26" s="24" t="s">
         <v>104</v>
       </c>
-      <c r="L26" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="M26" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="N26" s="23" t="s">
-        <v>10</v>
+      <c r="L26" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="M26" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="N26" s="24" t="s">
+        <v>104</v>
       </c>
       <c r="O26" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="P26" s="23" t="s">
-        <v>46</v>
+        <v>104</v>
+      </c>
+      <c r="P26" s="24" t="s">
+        <v>10</v>
       </c>
       <c r="Q26" s="23" t="s">
-        <v>104</v>
+        <v>10</v>
       </c>
       <c r="R26" s="23" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="S26" s="23"/>
       <c r="T26" s="23"/>
@@ -3041,8 +3069,8 @@
       <c r="AE26" s="23"/>
       <c r="AF26" s="23"/>
     </row>
-    <row r="27" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A27" s="40"/>
+    <row r="27" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A27" s="39"/>
       <c r="B27" s="7">
         <v>24</v>
       </c>
@@ -3058,35 +3086,35 @@
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
-      <c r="H27" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="I27" s="24" t="s">
-        <v>104</v>
+      <c r="H27" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="I27" s="23" t="s">
+        <v>46</v>
       </c>
       <c r="J27" s="24" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="K27" s="24" t="s">
         <v>104</v>
       </c>
-      <c r="L27" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="M27" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="N27" s="23" t="s">
+      <c r="L27" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="M27" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="N27" s="24" t="s">
         <v>10</v>
       </c>
       <c r="O27" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="P27" s="23" t="s">
-        <v>46</v>
+        <v>10</v>
+      </c>
+      <c r="P27" s="24" t="s">
+        <v>104</v>
       </c>
       <c r="Q27" s="23" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="R27" s="23" t="s">
         <v>46</v>
@@ -3106,8 +3134,8 @@
       <c r="AE27" s="23"/>
       <c r="AF27" s="23"/>
     </row>
-    <row r="28" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A28" s="58" t="s">
+    <row r="28" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A28" s="43" t="s">
         <v>10</v>
       </c>
       <c r="B28" s="7">
@@ -3125,10 +3153,10 @@
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
-      <c r="H28" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="I28" s="24" t="s">
+      <c r="H28" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="I28" s="23" t="s">
         <v>46</v>
       </c>
       <c r="J28" s="24" t="s">
@@ -3137,19 +3165,19 @@
       <c r="K28" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="L28" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="M28" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="N28" s="23" t="s">
+      <c r="L28" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="M28" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="N28" s="24" t="s">
         <v>46</v>
       </c>
       <c r="O28" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="P28" s="23" t="s">
+      <c r="P28" s="24" t="s">
         <v>46</v>
       </c>
       <c r="Q28" s="23" t="s">
@@ -3173,8 +3201,8 @@
       <c r="AE28" s="23"/>
       <c r="AF28" s="23"/>
     </row>
-    <row r="29" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A29" s="39"/>
+    <row r="29" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A29" s="38"/>
       <c r="B29" s="7">
         <v>26</v>
       </c>
@@ -3190,38 +3218,38 @@
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
-      <c r="H29" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="I29" s="24" t="s">
-        <v>104</v>
+      <c r="H29" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="I29" s="23" t="s">
+        <v>46</v>
       </c>
       <c r="J29" s="24" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="K29" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="L29" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="M29" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="N29" s="23" t="s">
-        <v>10</v>
+        <v>10</v>
+      </c>
+      <c r="L29" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="M29" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="N29" s="24" t="s">
+        <v>104</v>
       </c>
       <c r="O29" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="P29" s="23" t="s">
-        <v>10</v>
+      <c r="P29" s="24" t="s">
+        <v>104</v>
       </c>
       <c r="Q29" s="23" t="s">
         <v>10</v>
       </c>
       <c r="R29" s="23" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="S29" s="23"/>
       <c r="T29" s="23"/>
@@ -3238,8 +3266,8 @@
       <c r="AE29" s="23"/>
       <c r="AF29" s="23"/>
     </row>
-    <row r="30" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A30" s="39"/>
+    <row r="30" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A30" s="38"/>
       <c r="B30" s="7">
         <v>27</v>
       </c>
@@ -3255,10 +3283,10 @@
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
-      <c r="H30" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="I30" s="24" t="s">
+      <c r="H30" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="I30" s="23" t="s">
         <v>46</v>
       </c>
       <c r="J30" s="24" t="s">
@@ -3267,19 +3295,19 @@
       <c r="K30" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="L30" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="M30" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="N30" s="23" t="s">
+      <c r="L30" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="M30" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="N30" s="24" t="s">
         <v>46</v>
       </c>
       <c r="O30" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="P30" s="23" t="s">
+      <c r="P30" s="24" t="s">
         <v>46</v>
       </c>
       <c r="Q30" s="23" t="s">
@@ -3303,8 +3331,8 @@
       <c r="AE30" s="23"/>
       <c r="AF30" s="23"/>
     </row>
-    <row r="31" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A31" s="39"/>
+    <row r="31" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A31" s="38"/>
       <c r="B31" s="7">
         <v>28</v>
       </c>
@@ -3320,38 +3348,38 @@
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
-      <c r="H31" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="I31" s="24" t="s">
-        <v>46</v>
+      <c r="H31" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="I31" s="23" t="s">
+        <v>104</v>
       </c>
       <c r="J31" s="24" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="K31" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="L31" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="M31" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="N31" s="23" t="s">
-        <v>104</v>
+      <c r="L31" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="M31" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="N31" s="24" t="s">
+        <v>46</v>
       </c>
       <c r="O31" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="P31" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="P31" s="24" t="s">
         <v>46</v>
       </c>
       <c r="Q31" s="23" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="R31" s="23" t="s">
-        <v>104</v>
+        <v>46</v>
       </c>
       <c r="S31" s="23"/>
       <c r="T31" s="23"/>
@@ -3368,8 +3396,8 @@
       <c r="AE31" s="23"/>
       <c r="AF31" s="23"/>
     </row>
-    <row r="32" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A32" s="39"/>
+    <row r="32" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A32" s="38"/>
       <c r="B32" s="7">
         <v>29</v>
       </c>
@@ -3385,35 +3413,35 @@
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
-      <c r="H32" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="I32" s="24" t="s">
-        <v>10</v>
+      <c r="H32" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="I32" s="23" t="s">
+        <v>104</v>
       </c>
       <c r="J32" s="24" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="K32" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="L32" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="M32" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="N32" s="23" t="s">
-        <v>104</v>
+        <v>104</v>
+      </c>
+      <c r="L32" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="M32" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="N32" s="24" t="s">
+        <v>10</v>
       </c>
       <c r="O32" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="P32" s="23" t="s">
-        <v>104</v>
+        <v>10</v>
+      </c>
+      <c r="P32" s="24" t="s">
+        <v>10</v>
       </c>
       <c r="Q32" s="23" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="R32" s="23" t="s">
         <v>104</v>
@@ -3433,8 +3461,8 @@
       <c r="AE32" s="23"/>
       <c r="AF32" s="23"/>
     </row>
-    <row r="33" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A33" s="40"/>
+    <row r="33" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A33" s="39"/>
       <c r="B33" s="7">
         <v>30</v>
       </c>
@@ -3450,11 +3478,11 @@
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
-      <c r="H33" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="I33" s="24" t="s">
-        <v>46</v>
+      <c r="H33" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="I33" s="23" t="s">
+        <v>104</v>
       </c>
       <c r="J33" s="24" t="s">
         <v>104</v>
@@ -3462,20 +3490,20 @@
       <c r="K33" s="24" t="s">
         <v>104</v>
       </c>
-      <c r="L33" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="M33" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="N33" s="23" t="s">
-        <v>104</v>
+      <c r="L33" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="M33" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="N33" s="24" t="s">
+        <v>10</v>
       </c>
       <c r="O33" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="P33" s="23" t="s">
-        <v>104</v>
+      <c r="P33" s="24" t="s">
+        <v>46</v>
       </c>
       <c r="Q33" s="23" t="s">
         <v>104</v>
@@ -3498,8 +3526,8 @@
       <c r="AE33" s="23"/>
       <c r="AF33" s="23"/>
     </row>
-    <row r="34" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A34" s="56" t="s">
+    <row r="34" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A34" s="41" t="s">
         <v>11</v>
       </c>
       <c r="B34" s="7">
@@ -3517,38 +3545,38 @@
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
-      <c r="H34" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="I34" s="24" t="s">
-        <v>46</v>
+      <c r="H34" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="I34" s="23" t="s">
+        <v>104</v>
       </c>
       <c r="J34" s="24" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="K34" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="L34" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="M34" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="N34" s="23" t="s">
-        <v>10</v>
+        <v>10</v>
+      </c>
+      <c r="L34" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="M34" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="N34" s="24" t="s">
+        <v>104</v>
       </c>
       <c r="O34" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="P34" s="23" t="s">
-        <v>10</v>
+        <v>104</v>
+      </c>
+      <c r="P34" s="24" t="s">
+        <v>46</v>
       </c>
       <c r="Q34" s="23" t="s">
-        <v>104</v>
+        <v>46</v>
       </c>
       <c r="R34" s="23" t="s">
-        <v>104</v>
+        <v>10</v>
       </c>
       <c r="S34" s="23"/>
       <c r="T34" s="23"/>
@@ -3565,8 +3593,8 @@
       <c r="AE34" s="23"/>
       <c r="AF34" s="23"/>
     </row>
-    <row r="35" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A35" s="39"/>
+    <row r="35" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A35" s="38"/>
       <c r="B35" s="7">
         <v>32</v>
       </c>
@@ -3582,10 +3610,10 @@
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
-      <c r="H35" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="I35" s="24" t="s">
+      <c r="H35" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="I35" s="23" t="s">
         <v>46</v>
       </c>
       <c r="J35" s="24" t="s">
@@ -3594,26 +3622,26 @@
       <c r="K35" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="L35" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="M35" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="N35" s="23" t="s">
+      <c r="L35" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="M35" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="N35" s="24" t="s">
         <v>46</v>
       </c>
       <c r="O35" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="P35" s="23" t="s">
-        <v>10</v>
+      <c r="P35" s="24" t="s">
+        <v>46</v>
       </c>
       <c r="Q35" s="23" t="s">
         <v>46</v>
       </c>
       <c r="R35" s="23" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="S35" s="23"/>
       <c r="T35" s="23"/>
@@ -3630,8 +3658,8 @@
       <c r="AE35" s="23"/>
       <c r="AF35" s="23"/>
     </row>
-    <row r="36" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A36" s="39"/>
+    <row r="36" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A36" s="38"/>
       <c r="B36" s="7">
         <v>33</v>
       </c>
@@ -3647,31 +3675,31 @@
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
-      <c r="H36" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="I36" s="24" t="s">
+      <c r="H36" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="I36" s="23" t="s">
         <v>46</v>
       </c>
       <c r="J36" s="24" t="s">
-        <v>46</v>
+        <v>104</v>
       </c>
       <c r="K36" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="L36" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="M36" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="N36" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="L36" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="M36" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="N36" s="24" t="s">
         <v>46</v>
       </c>
       <c r="O36" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="P36" s="23" t="s">
+      <c r="P36" s="24" t="s">
         <v>46</v>
       </c>
       <c r="Q36" s="23" t="s">
@@ -3695,8 +3723,8 @@
       <c r="AE36" s="23"/>
       <c r="AF36" s="23"/>
     </row>
-    <row r="37" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A37" s="39"/>
+    <row r="37" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A37" s="38"/>
       <c r="B37" s="7">
         <v>34</v>
       </c>
@@ -3712,10 +3740,10 @@
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
-      <c r="H37" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="I37" s="24" t="s">
+      <c r="H37" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="I37" s="23" t="s">
         <v>104</v>
       </c>
       <c r="J37" s="24" t="s">
@@ -3724,26 +3752,26 @@
       <c r="K37" s="24" t="s">
         <v>104</v>
       </c>
-      <c r="L37" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="M37" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="N37" s="23" t="s">
+      <c r="L37" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="M37" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="N37" s="24" t="s">
         <v>104</v>
       </c>
       <c r="O37" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="P37" s="23" t="s">
-        <v>10</v>
+      <c r="P37" s="24" t="s">
+        <v>104</v>
       </c>
       <c r="Q37" s="23" t="s">
         <v>104</v>
       </c>
       <c r="R37" s="23" t="s">
-        <v>104</v>
+        <v>10</v>
       </c>
       <c r="S37" s="23"/>
       <c r="T37" s="23"/>
@@ -3760,8 +3788,8 @@
       <c r="AE37" s="23"/>
       <c r="AF37" s="23"/>
     </row>
-    <row r="38" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A38" s="39"/>
+    <row r="38" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A38" s="38"/>
       <c r="B38" s="7">
         <v>35</v>
       </c>
@@ -3777,38 +3805,38 @@
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
-      <c r="H38" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="I38" s="24" t="s">
+      <c r="H38" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="I38" s="23" t="s">
         <v>10</v>
       </c>
       <c r="J38" s="24" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="K38" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="L38" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="M38" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="N38" s="23" t="s">
-        <v>46</v>
+      <c r="L38" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="M38" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="N38" s="24" t="s">
+        <v>104</v>
       </c>
       <c r="O38" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="P38" s="23" t="s">
-        <v>46</v>
+      <c r="P38" s="24" t="s">
+        <v>10</v>
       </c>
       <c r="Q38" s="23" t="s">
         <v>10</v>
       </c>
       <c r="R38" s="23" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="S38" s="23"/>
       <c r="T38" s="23"/>
@@ -3825,8 +3853,8 @@
       <c r="AE38" s="23"/>
       <c r="AF38" s="23"/>
     </row>
-    <row r="39" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A39" s="40"/>
+    <row r="39" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A39" s="39"/>
       <c r="B39" s="7">
         <v>36</v>
       </c>
@@ -3842,32 +3870,32 @@
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
-      <c r="H39" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="I39" s="24" t="s">
-        <v>104</v>
+      <c r="H39" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="I39" s="23" t="s">
+        <v>10</v>
       </c>
       <c r="J39" s="24" t="s">
-        <v>104</v>
+        <v>10</v>
       </c>
       <c r="K39" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="L39" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="M39" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="N39" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="L39" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="M39" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="N39" s="24" t="s">
         <v>104</v>
       </c>
       <c r="O39" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="P39" s="23" t="s">
-        <v>10</v>
+      <c r="P39" s="24" t="s">
+        <v>104</v>
       </c>
       <c r="Q39" s="23" t="s">
         <v>104</v>
@@ -3890,8 +3918,8 @@
       <c r="AE39" s="23"/>
       <c r="AF39" s="23"/>
     </row>
-    <row r="40" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A40" s="55" t="s">
+    <row r="40" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A40" s="40" t="s">
         <v>12</v>
       </c>
       <c r="B40" s="7">
@@ -3909,11 +3937,11 @@
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
-      <c r="H40" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="I40" s="24" t="s">
-        <v>104</v>
+      <c r="H40" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="I40" s="23" t="s">
+        <v>46</v>
       </c>
       <c r="J40" s="24" t="s">
         <v>46</v>
@@ -3921,20 +3949,20 @@
       <c r="K40" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="L40" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="M40" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="N40" s="23" t="s">
+      <c r="L40" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="M40" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="N40" s="24" t="s">
         <v>46</v>
       </c>
       <c r="O40" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="P40" s="23" t="s">
-        <v>46</v>
+      <c r="P40" s="24" t="s">
+        <v>104</v>
       </c>
       <c r="Q40" s="23" t="s">
         <v>46</v>
@@ -3957,8 +3985,8 @@
       <c r="AE40" s="23"/>
       <c r="AF40" s="23"/>
     </row>
-    <row r="41" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A41" s="39"/>
+    <row r="41" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A41" s="38"/>
       <c r="B41" s="7">
         <v>38</v>
       </c>
@@ -3974,35 +4002,35 @@
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
-      <c r="H41" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="I41" s="24" t="s">
-        <v>104</v>
+      <c r="H41" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="I41" s="23" t="s">
+        <v>46</v>
       </c>
       <c r="J41" s="24" t="s">
-        <v>46</v>
+        <v>104</v>
       </c>
       <c r="K41" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="L41" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="M41" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="N41" s="23" t="s">
-        <v>10</v>
+        <v>10</v>
+      </c>
+      <c r="L41" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="M41" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="N41" s="24" t="s">
+        <v>104</v>
       </c>
       <c r="O41" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="P41" s="23" t="s">
-        <v>46</v>
+        <v>10</v>
+      </c>
+      <c r="P41" s="24" t="s">
+        <v>104</v>
       </c>
       <c r="Q41" s="23" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="R41" s="23" t="s">
         <v>46</v>
@@ -4022,8 +4050,8 @@
       <c r="AE41" s="23"/>
       <c r="AF41" s="23"/>
     </row>
-    <row r="42" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A42" s="39"/>
+    <row r="42" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A42" s="38"/>
       <c r="B42" s="7">
         <v>39</v>
       </c>
@@ -4039,11 +4067,11 @@
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
-      <c r="H42" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="I42" s="24" t="s">
-        <v>46</v>
+      <c r="H42" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="I42" s="23" t="s">
+        <v>10</v>
       </c>
       <c r="J42" s="24" t="s">
         <v>46</v>
@@ -4051,26 +4079,26 @@
       <c r="K42" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="L42" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="M42" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="N42" s="23" t="s">
+      <c r="L42" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="M42" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="N42" s="24" t="s">
         <v>46</v>
       </c>
       <c r="O42" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="P42" s="23" t="s">
+      <c r="P42" s="24" t="s">
         <v>46</v>
       </c>
       <c r="Q42" s="23" t="s">
         <v>46</v>
       </c>
       <c r="R42" s="23" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="S42" s="23"/>
       <c r="T42" s="23"/>
@@ -4087,8 +4115,8 @@
       <c r="AE42" s="23"/>
       <c r="AF42" s="23"/>
     </row>
-    <row r="43" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A43" s="39"/>
+    <row r="43" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A43" s="38"/>
       <c r="B43" s="7">
         <v>40</v>
       </c>
@@ -4104,35 +4132,35 @@
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
-      <c r="H43" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="I43" s="24" t="s">
-        <v>10</v>
+      <c r="H43" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="I43" s="23" t="s">
+        <v>104</v>
       </c>
       <c r="J43" s="24" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="K43" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="L43" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="M43" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="N43" s="23" t="s">
+      <c r="L43" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="M43" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="N43" s="24" t="s">
         <v>10</v>
       </c>
       <c r="O43" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="P43" s="23" t="s">
-        <v>104</v>
+        <v>46</v>
+      </c>
+      <c r="P43" s="24" t="s">
+        <v>10</v>
       </c>
       <c r="Q43" s="23" t="s">
-        <v>46</v>
+        <v>104</v>
       </c>
       <c r="R43" s="23" t="s">
         <v>104</v>
@@ -4152,8 +4180,8 @@
       <c r="AE43" s="23"/>
       <c r="AF43" s="23"/>
     </row>
-    <row r="44" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A44" s="39"/>
+    <row r="44" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A44" s="38"/>
       <c r="B44" s="7">
         <v>41</v>
       </c>
@@ -4169,38 +4197,38 @@
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
-      <c r="H44" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="I44" s="24" t="s">
-        <v>10</v>
+      <c r="H44" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="I44" s="23" t="s">
+        <v>104</v>
       </c>
       <c r="J44" s="24" t="s">
-        <v>46</v>
+        <v>104</v>
       </c>
       <c r="K44" s="24" t="s">
         <v>104</v>
       </c>
-      <c r="L44" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="M44" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="N44" s="23" t="s">
-        <v>104</v>
+      <c r="L44" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="M44" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="N44" s="24" t="s">
+        <v>10</v>
       </c>
       <c r="O44" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="P44" s="23" t="s">
+      <c r="P44" s="24" t="s">
         <v>10</v>
       </c>
       <c r="Q44" s="23" t="s">
         <v>10</v>
       </c>
       <c r="R44" s="23" t="s">
-        <v>104</v>
+        <v>10</v>
       </c>
       <c r="S44" s="23"/>
       <c r="T44" s="23"/>
@@ -4217,8 +4245,8 @@
       <c r="AE44" s="23"/>
       <c r="AF44" s="23"/>
     </row>
-    <row r="45" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A45" s="40"/>
+    <row r="45" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A45" s="39"/>
       <c r="B45" s="7">
         <v>42</v>
       </c>
@@ -4234,10 +4262,10 @@
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
-      <c r="H45" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="I45" s="24" t="s">
+      <c r="H45" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="I45" s="23" t="s">
         <v>104</v>
       </c>
       <c r="J45" s="24" t="s">
@@ -4246,19 +4274,19 @@
       <c r="K45" s="24" t="s">
         <v>104</v>
       </c>
-      <c r="L45" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="M45" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="N45" s="23" t="s">
+      <c r="L45" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="M45" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="N45" s="24" t="s">
         <v>104</v>
       </c>
       <c r="O45" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="P45" s="23" t="s">
+      <c r="P45" s="24" t="s">
         <v>104</v>
       </c>
       <c r="Q45" s="23" t="s">
@@ -4282,8 +4310,8 @@
       <c r="AE45" s="23"/>
       <c r="AF45" s="23"/>
     </row>
-    <row r="46" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A46" s="38" t="s">
+    <row r="46" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A46" s="57" t="s">
         <v>13</v>
       </c>
       <c r="B46" s="7">
@@ -4301,10 +4329,10 @@
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
-      <c r="H46" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="I46" s="24" t="s">
+      <c r="H46" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="I46" s="23" t="s">
         <v>46</v>
       </c>
       <c r="J46" s="24" t="s">
@@ -4313,19 +4341,19 @@
       <c r="K46" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="L46" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="M46" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="N46" s="23" t="s">
+      <c r="L46" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="M46" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="N46" s="24" t="s">
         <v>46</v>
       </c>
       <c r="O46" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="P46" s="23" t="s">
+      <c r="P46" s="24" t="s">
         <v>46</v>
       </c>
       <c r="Q46" s="23" t="s">
@@ -4349,8 +4377,8 @@
       <c r="AE46" s="23"/>
       <c r="AF46" s="23"/>
     </row>
-    <row r="47" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A47" s="39"/>
+    <row r="47" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A47" s="38"/>
       <c r="B47" s="7">
         <v>44</v>
       </c>
@@ -4366,10 +4394,10 @@
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
-      <c r="H47" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="I47" s="24" t="s">
+      <c r="H47" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="I47" s="23" t="s">
         <v>104</v>
       </c>
       <c r="J47" s="24" t="s">
@@ -4378,23 +4406,23 @@
       <c r="K47" s="24" t="s">
         <v>104</v>
       </c>
-      <c r="L47" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="M47" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="N47" s="23" t="s">
+      <c r="L47" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="M47" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="N47" s="24" t="s">
         <v>104</v>
       </c>
       <c r="O47" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="P47" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="P47" s="24" t="s">
         <v>104</v>
       </c>
       <c r="Q47" s="23" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="R47" s="23" t="s">
         <v>104</v>
@@ -4414,8 +4442,8 @@
       <c r="AE47" s="23"/>
       <c r="AF47" s="23"/>
     </row>
-    <row r="48" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A48" s="39"/>
+    <row r="48" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A48" s="38"/>
       <c r="B48" s="7">
         <v>45</v>
       </c>
@@ -4431,10 +4459,10 @@
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
-      <c r="H48" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="I48" s="24" t="s">
+      <c r="H48" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="I48" s="23" t="s">
         <v>46</v>
       </c>
       <c r="J48" s="24" t="s">
@@ -4443,19 +4471,19 @@
       <c r="K48" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="L48" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="M48" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="N48" s="23" t="s">
+      <c r="L48" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="M48" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="N48" s="24" t="s">
         <v>46</v>
       </c>
       <c r="O48" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="P48" s="23" t="s">
+      <c r="P48" s="24" t="s">
         <v>46</v>
       </c>
       <c r="Q48" s="23" t="s">
@@ -4479,8 +4507,8 @@
       <c r="AE48" s="23"/>
       <c r="AF48" s="23"/>
     </row>
-    <row r="49" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A49" s="39"/>
+    <row r="49" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A49" s="38"/>
       <c r="B49" s="7">
         <v>46</v>
       </c>
@@ -4496,11 +4524,11 @@
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
-      <c r="H49" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="I49" s="24" t="s">
-        <v>46</v>
+      <c r="H49" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="I49" s="23" t="s">
+        <v>104</v>
       </c>
       <c r="J49" s="24" t="s">
         <v>46</v>
@@ -4508,26 +4536,26 @@
       <c r="K49" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="L49" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="M49" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="N49" s="23" t="s">
+      <c r="L49" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="M49" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="N49" s="24" t="s">
         <v>46</v>
       </c>
       <c r="O49" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="P49" s="23" t="s">
+      <c r="P49" s="24" t="s">
         <v>46</v>
       </c>
       <c r="Q49" s="23" t="s">
         <v>46</v>
       </c>
       <c r="R49" s="23" t="s">
-        <v>104</v>
+        <v>46</v>
       </c>
       <c r="S49" s="23"/>
       <c r="T49" s="23"/>
@@ -4544,8 +4572,8 @@
       <c r="AE49" s="23"/>
       <c r="AF49" s="23"/>
     </row>
-    <row r="50" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A50" s="39"/>
+    <row r="50" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A50" s="38"/>
       <c r="B50" s="7">
         <v>47</v>
       </c>
@@ -4561,11 +4589,11 @@
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
-      <c r="H50" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="I50" s="24" t="s">
-        <v>10</v>
+      <c r="H50" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="I50" s="23" t="s">
+        <v>104</v>
       </c>
       <c r="J50" s="24" t="s">
         <v>10</v>
@@ -4573,26 +4601,26 @@
       <c r="K50" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="L50" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="M50" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="N50" s="23" t="s">
+      <c r="L50" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="M50" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="N50" s="24" t="s">
         <v>104</v>
       </c>
       <c r="O50" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="P50" s="23" t="s">
+      <c r="P50" s="24" t="s">
         <v>10</v>
       </c>
       <c r="Q50" s="23" t="s">
         <v>10</v>
       </c>
       <c r="R50" s="23" t="s">
-        <v>104</v>
+        <v>10</v>
       </c>
       <c r="S50" s="23"/>
       <c r="T50" s="23"/>
@@ -4609,8 +4637,8 @@
       <c r="AE50" s="23"/>
       <c r="AF50" s="23"/>
     </row>
-    <row r="51" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A51" s="40"/>
+    <row r="51" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A51" s="39"/>
       <c r="B51" s="7">
         <v>48</v>
       </c>
@@ -4626,31 +4654,31 @@
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
-      <c r="H51" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="I51" s="24" t="s">
+      <c r="H51" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="I51" s="23" t="s">
         <v>104</v>
       </c>
       <c r="J51" s="24" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="K51" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="L51" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="M51" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="N51" s="23" t="s">
-        <v>104</v>
+        <v>10</v>
+      </c>
+      <c r="L51" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="M51" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="N51" s="24" t="s">
+        <v>10</v>
       </c>
       <c r="O51" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="P51" s="23" t="s">
+      <c r="P51" s="24" t="s">
         <v>104</v>
       </c>
       <c r="Q51" s="23" t="s">
@@ -4674,8 +4702,8 @@
       <c r="AE51" s="23"/>
       <c r="AF51" s="23"/>
     </row>
-    <row r="52" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A52" s="45" t="s">
+    <row r="52" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A52" s="60" t="s">
         <v>77</v>
       </c>
       <c r="B52" s="7">
@@ -4693,38 +4721,38 @@
         <f t="shared" ref="G52:G75" si="2">IF(E52="","-",IF(E52&gt;F52,"L",IF(E52=F52,"E",IF(E52&lt;F52,"V"))))</f>
         <v>-</v>
       </c>
-      <c r="H52" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="I52" s="26" t="s">
+      <c r="H52" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="I52" s="25" t="s">
         <v>10</v>
       </c>
       <c r="J52" s="26" t="s">
-        <v>46</v>
+        <v>104</v>
       </c>
       <c r="K52" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="L52" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="M52" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="N52" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="L52" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="M52" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="N52" s="26" t="s">
         <v>46</v>
       </c>
       <c r="O52" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="P52" s="25" t="s">
-        <v>46</v>
+      <c r="P52" s="26" t="s">
+        <v>10</v>
       </c>
       <c r="Q52" s="25" t="s">
         <v>46</v>
       </c>
       <c r="R52" s="25" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="S52" s="25"/>
       <c r="T52" s="25"/>
@@ -4741,8 +4769,8 @@
       <c r="AE52" s="25"/>
       <c r="AF52" s="25"/>
     </row>
-    <row r="53" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A53" s="46"/>
+    <row r="53" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A53" s="61"/>
       <c r="B53" s="7">
         <v>50</v>
       </c>
@@ -4758,31 +4786,31 @@
         <f t="shared" si="2"/>
         <v>-</v>
       </c>
-      <c r="H53" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="I53" s="26" t="s">
+      <c r="H53" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="I53" s="25" t="s">
         <v>104</v>
       </c>
       <c r="J53" s="26" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="K53" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="L53" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="M53" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="N53" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="L53" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="M53" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="N53" s="26" t="s">
         <v>104</v>
       </c>
       <c r="O53" s="25" t="s">
         <v>104</v>
       </c>
-      <c r="P53" s="25" t="s">
+      <c r="P53" s="26" t="s">
         <v>104</v>
       </c>
       <c r="Q53" s="25" t="s">
@@ -4806,8 +4834,8 @@
       <c r="AE53" s="25"/>
       <c r="AF53" s="25"/>
     </row>
-    <row r="54" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A54" s="46"/>
+    <row r="54" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A54" s="61"/>
       <c r="B54" s="7">
         <v>51</v>
       </c>
@@ -4823,10 +4851,10 @@
         <f t="shared" si="2"/>
         <v>-</v>
       </c>
-      <c r="H54" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="I54" s="26" t="s">
+      <c r="H54" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="I54" s="25" t="s">
         <v>46</v>
       </c>
       <c r="J54" s="26" t="s">
@@ -4835,19 +4863,19 @@
       <c r="K54" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="L54" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="M54" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="N54" s="25" t="s">
+      <c r="L54" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="M54" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="N54" s="26" t="s">
         <v>46</v>
       </c>
       <c r="O54" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="P54" s="25" t="s">
+      <c r="P54" s="26" t="s">
         <v>46</v>
       </c>
       <c r="Q54" s="25" t="s">
@@ -4871,8 +4899,8 @@
       <c r="AE54" s="25"/>
       <c r="AF54" s="25"/>
     </row>
-    <row r="55" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A55" s="46"/>
+    <row r="55" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A55" s="61"/>
       <c r="B55" s="7">
         <v>52</v>
       </c>
@@ -4888,38 +4916,38 @@
         <f t="shared" si="2"/>
         <v>-</v>
       </c>
-      <c r="H55" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="I55" s="26" t="s">
-        <v>104</v>
+      <c r="H55" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="I55" s="25" t="s">
+        <v>10</v>
       </c>
       <c r="J55" s="26" t="s">
-        <v>46</v>
+        <v>104</v>
       </c>
       <c r="K55" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="L55" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="M55" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="N55" s="25" t="s">
-        <v>10</v>
+        <v>46</v>
+      </c>
+      <c r="L55" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="M55" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="N55" s="26" t="s">
+        <v>46</v>
       </c>
       <c r="O55" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="P55" s="25" t="s">
-        <v>46</v>
+        <v>46</v>
+      </c>
+      <c r="P55" s="26" t="s">
+        <v>104</v>
       </c>
       <c r="Q55" s="25" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="R55" s="25" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="S55" s="25"/>
       <c r="T55" s="25"/>
@@ -4937,8 +4965,8 @@
       <c r="AF55" s="25"/>
       <c r="AK55" s="31"/>
     </row>
-    <row r="56" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A56" s="46"/>
+    <row r="56" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A56" s="61"/>
       <c r="B56" s="7">
         <v>53</v>
       </c>
@@ -4954,10 +4982,10 @@
         <f t="shared" si="2"/>
         <v>-</v>
       </c>
-      <c r="H56" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="I56" s="26" t="s">
+      <c r="H56" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="I56" s="25" t="s">
         <v>10</v>
       </c>
       <c r="J56" s="26" t="s">
@@ -4966,26 +4994,26 @@
       <c r="K56" s="26" t="s">
         <v>104</v>
       </c>
-      <c r="L56" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="M56" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="N56" s="25" t="s">
-        <v>46</v>
+      <c r="L56" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="M56" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="N56" s="26" t="s">
+        <v>10</v>
       </c>
       <c r="O56" s="25" t="s">
         <v>104</v>
       </c>
-      <c r="P56" s="25" t="s">
-        <v>104</v>
+      <c r="P56" s="26" t="s">
+        <v>10</v>
       </c>
       <c r="Q56" s="25" t="s">
         <v>104</v>
       </c>
       <c r="R56" s="25" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="S56" s="25"/>
       <c r="T56" s="25"/>
@@ -5002,8 +5030,8 @@
       <c r="AE56" s="25"/>
       <c r="AF56" s="25"/>
     </row>
-    <row r="57" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A57" s="47"/>
+    <row r="57" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A57" s="62"/>
       <c r="B57" s="7">
         <v>54</v>
       </c>
@@ -5019,38 +5047,38 @@
         <f t="shared" si="2"/>
         <v>-</v>
       </c>
-      <c r="H57" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="I57" s="26" t="s">
+      <c r="H57" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="I57" s="25" t="s">
         <v>46</v>
       </c>
       <c r="J57" s="26" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="K57" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="L57" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="M57" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="N57" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="L57" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="M57" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="N57" s="26" t="s">
         <v>10</v>
       </c>
       <c r="O57" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="P57" s="25" t="s">
-        <v>10</v>
+        <v>10</v>
+      </c>
+      <c r="P57" s="26" t="s">
+        <v>46</v>
       </c>
       <c r="Q57" s="25" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="R57" s="25" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="S57" s="25"/>
       <c r="T57" s="25"/>
@@ -5067,8 +5095,8 @@
       <c r="AE57" s="25"/>
       <c r="AF57" s="25"/>
     </row>
-    <row r="58" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A58" s="48" t="s">
+    <row r="58" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A58" s="63" t="s">
         <v>78</v>
       </c>
       <c r="B58" s="7">
@@ -5086,11 +5114,11 @@
         <f t="shared" si="2"/>
         <v>-</v>
       </c>
-      <c r="H58" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="I58" s="26" t="s">
-        <v>46</v>
+      <c r="H58" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="I58" s="25" t="s">
+        <v>10</v>
       </c>
       <c r="J58" s="26" t="s">
         <v>46</v>
@@ -5098,26 +5126,26 @@
       <c r="K58" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="L58" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="M58" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="N58" s="25" t="s">
+      <c r="L58" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="M58" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="N58" s="26" t="s">
         <v>46</v>
       </c>
       <c r="O58" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="P58" s="25" t="s">
+      <c r="P58" s="26" t="s">
         <v>46</v>
       </c>
       <c r="Q58" s="25" t="s">
         <v>46</v>
       </c>
       <c r="R58" s="25" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="S58" s="25"/>
       <c r="T58" s="25"/>
@@ -5134,8 +5162,8 @@
       <c r="AE58" s="25"/>
       <c r="AF58" s="25"/>
     </row>
-    <row r="59" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A59" s="49"/>
+    <row r="59" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A59" s="64"/>
       <c r="B59" s="7">
         <v>56</v>
       </c>
@@ -5151,11 +5179,11 @@
         <f t="shared" si="2"/>
         <v>-</v>
       </c>
-      <c r="H59" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="I59" s="26" t="s">
-        <v>10</v>
+      <c r="H59" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="I59" s="25" t="s">
+        <v>46</v>
       </c>
       <c r="J59" s="26" t="s">
         <v>46</v>
@@ -5163,23 +5191,23 @@
       <c r="K59" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="L59" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="M59" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="N59" s="25" t="s">
+      <c r="L59" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="M59" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="N59" s="26" t="s">
         <v>46</v>
       </c>
       <c r="O59" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="P59" s="25" t="s">
-        <v>46</v>
+        <v>10</v>
+      </c>
+      <c r="P59" s="26" t="s">
+        <v>10</v>
       </c>
       <c r="Q59" s="25" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="R59" s="25" t="s">
         <v>46</v>
@@ -5199,8 +5227,8 @@
       <c r="AE59" s="25"/>
       <c r="AF59" s="25"/>
     </row>
-    <row r="60" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A60" s="49"/>
+    <row r="60" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A60" s="64"/>
       <c r="B60" s="7">
         <v>57</v>
       </c>
@@ -5216,31 +5244,31 @@
         <f t="shared" si="2"/>
         <v>-</v>
       </c>
-      <c r="H60" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="I60" s="26" t="s">
+      <c r="H60" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="I60" s="25" t="s">
         <v>46</v>
       </c>
       <c r="J60" s="26" t="s">
         <v>46</v>
       </c>
       <c r="K60" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="L60" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="M60" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="N60" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="L60" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="M60" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="N60" s="26" t="s">
         <v>46</v>
       </c>
       <c r="O60" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="P60" s="25" t="s">
+      <c r="P60" s="26" t="s">
         <v>46</v>
       </c>
       <c r="Q60" s="25" t="s">
@@ -5264,8 +5292,8 @@
       <c r="AE60" s="25"/>
       <c r="AF60" s="25"/>
     </row>
-    <row r="61" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A61" s="49"/>
+    <row r="61" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A61" s="64"/>
       <c r="B61" s="7">
         <v>58</v>
       </c>
@@ -5281,35 +5309,35 @@
         <f t="shared" si="2"/>
         <v>-</v>
       </c>
-      <c r="H61" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="I61" s="26" t="s">
-        <v>46</v>
+      <c r="H61" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="I61" s="25" t="s">
+        <v>104</v>
       </c>
       <c r="J61" s="26" t="s">
         <v>10</v>
       </c>
       <c r="K61" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="L61" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="M61" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="N61" s="25" t="s">
-        <v>104</v>
+        <v>46</v>
+      </c>
+      <c r="L61" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="M61" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="N61" s="26" t="s">
+        <v>46</v>
       </c>
       <c r="O61" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="P61" s="25" t="s">
-        <v>104</v>
+        <v>10</v>
+      </c>
+      <c r="P61" s="26" t="s">
+        <v>46</v>
       </c>
       <c r="Q61" s="25" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="R61" s="25" t="s">
         <v>104</v>
@@ -5329,8 +5357,8 @@
       <c r="AE61" s="25"/>
       <c r="AF61" s="25"/>
     </row>
-    <row r="62" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A62" s="49"/>
+    <row r="62" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A62" s="64"/>
       <c r="B62" s="7">
         <v>59</v>
       </c>
@@ -5346,35 +5374,35 @@
         <f t="shared" si="2"/>
         <v>-</v>
       </c>
-      <c r="H62" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="I62" s="26" t="s">
+      <c r="H62" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="I62" s="25" t="s">
         <v>10</v>
       </c>
       <c r="J62" s="26" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="K62" s="26" t="s">
         <v>104</v>
       </c>
-      <c r="L62" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="M62" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="N62" s="25" t="s">
+      <c r="L62" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="M62" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="N62" s="26" t="s">
         <v>104</v>
       </c>
       <c r="O62" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="P62" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="P62" s="26" t="s">
         <v>10</v>
       </c>
       <c r="Q62" s="25" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="R62" s="25" t="s">
         <v>10</v>
@@ -5394,8 +5422,8 @@
       <c r="AE62" s="25"/>
       <c r="AF62" s="25"/>
     </row>
-    <row r="63" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A63" s="50"/>
+    <row r="63" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A63" s="65"/>
       <c r="B63" s="7">
         <v>60</v>
       </c>
@@ -5411,10 +5439,10 @@
         <f t="shared" si="2"/>
         <v>-</v>
       </c>
-      <c r="H63" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="I63" s="26" t="s">
+      <c r="H63" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="I63" s="25" t="s">
         <v>104</v>
       </c>
       <c r="J63" s="26" t="s">
@@ -5423,19 +5451,19 @@
       <c r="K63" s="26" t="s">
         <v>104</v>
       </c>
-      <c r="L63" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="M63" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="N63" s="25" t="s">
+      <c r="L63" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="M63" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="N63" s="26" t="s">
         <v>104</v>
       </c>
       <c r="O63" s="25" t="s">
         <v>104</v>
       </c>
-      <c r="P63" s="25" t="s">
+      <c r="P63" s="26" t="s">
         <v>104</v>
       </c>
       <c r="Q63" s="25" t="s">
@@ -5459,8 +5487,8 @@
       <c r="AE63" s="25"/>
       <c r="AF63" s="25"/>
     </row>
-    <row r="64" spans="1:37" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A64" s="32" t="s">
+    <row r="64" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A64" s="51" t="s">
         <v>79</v>
       </c>
       <c r="B64" s="7">
@@ -5478,10 +5506,10 @@
         <f t="shared" si="2"/>
         <v>-</v>
       </c>
-      <c r="H64" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="I64" s="26" t="s">
+      <c r="H64" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="I64" s="25" t="s">
         <v>46</v>
       </c>
       <c r="J64" s="26" t="s">
@@ -5490,19 +5518,19 @@
       <c r="K64" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="L64" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="M64" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="N64" s="25" t="s">
+      <c r="L64" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="M64" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="N64" s="26" t="s">
         <v>46</v>
       </c>
       <c r="O64" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="P64" s="25" t="s">
+      <c r="P64" s="26" t="s">
         <v>46</v>
       </c>
       <c r="Q64" s="25" t="s">
@@ -5526,8 +5554,8 @@
       <c r="AE64" s="25"/>
       <c r="AF64" s="25"/>
     </row>
-    <row r="65" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A65" s="33"/>
+    <row r="65" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A65" s="52"/>
       <c r="B65" s="7">
         <v>62</v>
       </c>
@@ -5543,10 +5571,10 @@
         <f t="shared" si="2"/>
         <v>-</v>
       </c>
-      <c r="H65" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="I65" s="26" t="s">
+      <c r="H65" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="I65" s="25" t="s">
         <v>104</v>
       </c>
       <c r="J65" s="26" t="s">
@@ -5555,19 +5583,19 @@
       <c r="K65" s="26" t="s">
         <v>104</v>
       </c>
-      <c r="L65" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="M65" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="N65" s="25" t="s">
+      <c r="L65" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="M65" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="N65" s="26" t="s">
         <v>104</v>
       </c>
       <c r="O65" s="25" t="s">
         <v>104</v>
       </c>
-      <c r="P65" s="25" t="s">
+      <c r="P65" s="26" t="s">
         <v>104</v>
       </c>
       <c r="Q65" s="25" t="s">
@@ -5591,8 +5619,8 @@
       <c r="AE65" s="25"/>
       <c r="AF65" s="25"/>
     </row>
-    <row r="66" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A66" s="33"/>
+    <row r="66" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A66" s="52"/>
       <c r="B66" s="7">
         <v>63</v>
       </c>
@@ -5608,10 +5636,10 @@
         <f t="shared" si="2"/>
         <v>-</v>
       </c>
-      <c r="H66" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="I66" s="26" t="s">
+      <c r="H66" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="I66" s="25" t="s">
         <v>46</v>
       </c>
       <c r="J66" s="26" t="s">
@@ -5620,19 +5648,19 @@
       <c r="K66" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="L66" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="M66" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="N66" s="25" t="s">
+      <c r="L66" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="M66" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="N66" s="26" t="s">
         <v>46</v>
       </c>
       <c r="O66" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="P66" s="25" t="s">
+      <c r="P66" s="26" t="s">
         <v>46</v>
       </c>
       <c r="Q66" s="25" t="s">
@@ -5656,8 +5684,8 @@
       <c r="AE66" s="25"/>
       <c r="AF66" s="25"/>
     </row>
-    <row r="67" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A67" s="33"/>
+    <row r="67" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A67" s="52"/>
       <c r="B67" s="7">
         <v>64</v>
       </c>
@@ -5673,10 +5701,10 @@
         <f t="shared" si="2"/>
         <v>-</v>
       </c>
-      <c r="H67" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="I67" s="26" t="s">
+      <c r="H67" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="I67" s="25" t="s">
         <v>46</v>
       </c>
       <c r="J67" s="26" t="s">
@@ -5685,19 +5713,19 @@
       <c r="K67" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="L67" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="M67" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="N67" s="25" t="s">
-        <v>104</v>
+      <c r="L67" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="M67" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="N67" s="26" t="s">
+        <v>46</v>
       </c>
       <c r="O67" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="P67" s="25" t="s">
+      <c r="P67" s="26" t="s">
         <v>46</v>
       </c>
       <c r="Q67" s="25" t="s">
@@ -5721,8 +5749,8 @@
       <c r="AE67" s="25"/>
       <c r="AF67" s="25"/>
     </row>
-    <row r="68" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A68" s="33"/>
+    <row r="68" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A68" s="52"/>
       <c r="B68" s="7">
         <v>65</v>
       </c>
@@ -5738,32 +5766,32 @@
         <f t="shared" si="2"/>
         <v>-</v>
       </c>
-      <c r="H68" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="I68" s="26" t="s">
-        <v>46</v>
+      <c r="H68" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="I68" s="25" t="s">
+        <v>10</v>
       </c>
       <c r="J68" s="26" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="K68" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="L68" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="M68" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="N68" s="25" t="s">
-        <v>46</v>
+        <v>10</v>
+      </c>
+      <c r="L68" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="M68" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="N68" s="26" t="s">
+        <v>104</v>
       </c>
       <c r="O68" s="25" t="s">
         <v>104</v>
       </c>
-      <c r="P68" s="25" t="s">
-        <v>10</v>
+      <c r="P68" s="26" t="s">
+        <v>46</v>
       </c>
       <c r="Q68" s="25" t="s">
         <v>104</v>
@@ -5786,8 +5814,8 @@
       <c r="AE68" s="25"/>
       <c r="AF68" s="25"/>
     </row>
-    <row r="69" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A69" s="34"/>
+    <row r="69" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A69" s="53"/>
       <c r="B69" s="7">
         <v>66</v>
       </c>
@@ -5803,38 +5831,38 @@
         <f t="shared" si="2"/>
         <v>-</v>
       </c>
-      <c r="H69" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="I69" s="26" t="s">
-        <v>46</v>
+      <c r="H69" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="I69" s="25" t="s">
+        <v>104</v>
       </c>
       <c r="J69" s="26" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="K69" s="26" t="s">
         <v>104</v>
       </c>
-      <c r="L69" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="M69" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="N69" s="25" t="s">
-        <v>46</v>
+      <c r="L69" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="M69" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="N69" s="26" t="s">
+        <v>104</v>
       </c>
       <c r="O69" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="P69" s="25" t="s">
-        <v>10</v>
+      <c r="P69" s="26" t="s">
+        <v>46</v>
       </c>
       <c r="Q69" s="25" t="s">
         <v>10</v>
       </c>
       <c r="R69" s="25" t="s">
-        <v>104</v>
+        <v>10</v>
       </c>
       <c r="S69" s="25"/>
       <c r="T69" s="25"/>
@@ -5851,8 +5879,8 @@
       <c r="AE69" s="25"/>
       <c r="AF69" s="25"/>
     </row>
-    <row r="70" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A70" s="35" t="s">
+    <row r="70" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A70" s="54" t="s">
         <v>46</v>
       </c>
       <c r="B70" s="7">
@@ -5870,35 +5898,35 @@
         <f t="shared" si="2"/>
         <v>-</v>
       </c>
-      <c r="H70" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="I70" s="26" t="s">
-        <v>104</v>
+      <c r="H70" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="I70" s="25" t="s">
+        <v>46</v>
       </c>
       <c r="J70" s="26" t="s">
-        <v>104</v>
+        <v>46</v>
       </c>
       <c r="K70" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="L70" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="M70" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="N70" s="25" t="s">
-        <v>10</v>
+      <c r="L70" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="M70" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="N70" s="26" t="s">
+        <v>104</v>
       </c>
       <c r="O70" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="P70" s="25" t="s">
-        <v>46</v>
+        <v>46</v>
+      </c>
+      <c r="P70" s="26" t="s">
+        <v>104</v>
       </c>
       <c r="Q70" s="25" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="R70" s="25" t="s">
         <v>46</v>
@@ -5918,8 +5946,8 @@
       <c r="AE70" s="25"/>
       <c r="AF70" s="25"/>
     </row>
-    <row r="71" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A71" s="36"/>
+    <row r="71" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A71" s="55"/>
       <c r="B71" s="7">
         <v>68</v>
       </c>
@@ -5935,38 +5963,38 @@
         <f t="shared" si="2"/>
         <v>-</v>
       </c>
-      <c r="H71" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="I71" s="26" t="s">
-        <v>10</v>
+      <c r="H71" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="I71" s="25" t="s">
+        <v>46</v>
       </c>
       <c r="J71" s="26" t="s">
-        <v>46</v>
+        <v>104</v>
       </c>
       <c r="K71" s="26" t="s">
         <v>104</v>
       </c>
-      <c r="L71" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="M71" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="N71" s="25" t="s">
-        <v>10</v>
+      <c r="L71" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="M71" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="N71" s="26" t="s">
+        <v>104</v>
       </c>
       <c r="O71" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="P71" s="25" t="s">
-        <v>104</v>
+        <v>10</v>
+      </c>
+      <c r="P71" s="26" t="s">
+        <v>10</v>
       </c>
       <c r="Q71" s="25" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="R71" s="25" t="s">
-        <v>46</v>
+        <v>104</v>
       </c>
       <c r="S71" s="25"/>
       <c r="T71" s="25"/>
@@ -5983,8 +6011,8 @@
       <c r="AE71" s="25"/>
       <c r="AF71" s="25"/>
     </row>
-    <row r="72" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A72" s="36"/>
+    <row r="72" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A72" s="55"/>
       <c r="B72" s="7">
         <v>69</v>
       </c>
@@ -6000,11 +6028,11 @@
         <f t="shared" si="2"/>
         <v>-</v>
       </c>
-      <c r="H72" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="I72" s="26" t="s">
-        <v>46</v>
+      <c r="H72" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="I72" s="25" t="s">
+        <v>10</v>
       </c>
       <c r="J72" s="26" t="s">
         <v>46</v>
@@ -6012,26 +6040,26 @@
       <c r="K72" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="L72" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="M72" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="N72" s="25" t="s">
+      <c r="L72" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="M72" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="N72" s="26" t="s">
         <v>46</v>
       </c>
       <c r="O72" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="P72" s="25" t="s">
+      <c r="P72" s="26" t="s">
         <v>46</v>
       </c>
       <c r="Q72" s="25" t="s">
         <v>46</v>
       </c>
       <c r="R72" s="25" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="S72" s="25"/>
       <c r="T72" s="25"/>
@@ -6048,8 +6076,8 @@
       <c r="AE72" s="25"/>
       <c r="AF72" s="25"/>
     </row>
-    <row r="73" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A73" s="36"/>
+    <row r="73" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A73" s="55"/>
       <c r="B73" s="7">
         <v>70</v>
       </c>
@@ -6065,38 +6093,38 @@
         <f t="shared" si="2"/>
         <v>-</v>
       </c>
-      <c r="H73" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="I73" s="26" t="s">
-        <v>10</v>
+      <c r="H73" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="I73" s="25" t="s">
+        <v>104</v>
       </c>
       <c r="J73" s="26" t="s">
         <v>104</v>
       </c>
       <c r="K73" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="L73" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="M73" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="N73" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="L73" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="M73" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="N73" s="26" t="s">
         <v>104</v>
       </c>
       <c r="O73" s="25" t="s">
         <v>104</v>
       </c>
-      <c r="P73" s="25" t="s">
+      <c r="P73" s="26" t="s">
         <v>10</v>
       </c>
       <c r="Q73" s="25" t="s">
         <v>104</v>
       </c>
       <c r="R73" s="25" t="s">
-        <v>104</v>
+        <v>10</v>
       </c>
       <c r="S73" s="25"/>
       <c r="T73" s="25"/>
@@ -6113,8 +6141,8 @@
       <c r="AE73" s="25"/>
       <c r="AF73" s="25"/>
     </row>
-    <row r="74" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A74" s="36"/>
+    <row r="74" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A74" s="55"/>
       <c r="B74" s="7">
         <v>71</v>
       </c>
@@ -6130,38 +6158,38 @@
         <f t="shared" si="2"/>
         <v>-</v>
       </c>
-      <c r="H74" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="I74" s="26" t="s">
-        <v>104</v>
+      <c r="H74" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="I74" s="25" t="s">
+        <v>10</v>
       </c>
       <c r="J74" s="26" t="s">
-        <v>104</v>
+        <v>46</v>
       </c>
       <c r="K74" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="L74" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="M74" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="N74" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="L74" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="M74" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="N74" s="26" t="s">
         <v>104</v>
       </c>
       <c r="O74" s="25" t="s">
         <v>104</v>
       </c>
-      <c r="P74" s="25" t="s">
+      <c r="P74" s="26" t="s">
         <v>104</v>
       </c>
       <c r="Q74" s="25" t="s">
         <v>104</v>
       </c>
       <c r="R74" s="25" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="S74" s="25"/>
       <c r="T74" s="25"/>
@@ -6178,8 +6206,8 @@
       <c r="AE74" s="25"/>
       <c r="AF74" s="25"/>
     </row>
-    <row r="75" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A75" s="37"/>
+    <row r="75" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A75" s="56"/>
       <c r="B75" s="7">
         <v>72</v>
       </c>
@@ -6195,38 +6223,38 @@
         <f t="shared" si="2"/>
         <v>-</v>
       </c>
-      <c r="H75" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="I75" s="26" t="s">
-        <v>46</v>
+      <c r="H75" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="I75" s="25" t="s">
+        <v>104</v>
       </c>
       <c r="J75" s="26" t="s">
         <v>46</v>
       </c>
       <c r="K75" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="L75" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="M75" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="N75" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="L75" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="M75" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="N75" s="26" t="s">
         <v>46</v>
       </c>
       <c r="O75" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="P75" s="25" t="s">
-        <v>10</v>
+      <c r="P75" s="26" t="s">
+        <v>46</v>
       </c>
       <c r="Q75" s="25" t="s">
         <v>46</v>
       </c>
       <c r="R75" s="25" t="s">
-        <v>104</v>
+        <v>10</v>
       </c>
       <c r="S75" s="25"/>
       <c r="T75" s="25"/>
@@ -6243,51 +6271,51 @@
       <c r="AE75" s="25"/>
       <c r="AF75" s="25"/>
     </row>
-    <row r="76" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A76" s="27"/>
       <c r="B76" s="27"/>
       <c r="C76" s="27"/>
-      <c r="D76" s="41" t="s">
+      <c r="D76" s="58" t="s">
         <v>14</v>
       </c>
-      <c r="E76" s="42"/>
-      <c r="F76" s="43"/>
+      <c r="E76" s="33"/>
+      <c r="F76" s="34"/>
       <c r="G76" s="2">
         <f>SUM(E4:F75)</f>
-        <v>0</v>
-      </c>
-      <c r="H76" s="25">
+        <v>19</v>
+      </c>
+      <c r="H76" s="26">
+        <v>179</v>
+      </c>
+      <c r="I76" s="25">
+        <v>186</v>
+      </c>
+      <c r="J76" s="26">
+        <v>185</v>
+      </c>
+      <c r="K76" s="26">
+        <v>201</v>
+      </c>
+      <c r="L76" s="25">
+        <v>222</v>
+      </c>
+      <c r="M76" s="25">
         <v>172</v>
       </c>
-      <c r="I76" s="26">
+      <c r="N76" s="26">
+        <v>162</v>
+      </c>
+      <c r="O76" s="25">
+        <v>190</v>
+      </c>
+      <c r="P76" s="26">
         <v>180</v>
       </c>
-      <c r="J76" s="26">
-        <v>179</v>
-      </c>
-      <c r="K76" s="26">
-        <v>185</v>
-      </c>
-      <c r="L76" s="26">
-        <v>201</v>
-      </c>
-      <c r="M76" s="26">
-        <v>162</v>
-      </c>
-      <c r="N76" s="25">
-        <v>222</v>
-      </c>
-      <c r="O76" s="25">
+      <c r="Q76" s="25">
         <v>197</v>
       </c>
-      <c r="P76" s="25">
+      <c r="R76" s="25">
         <v>169</v>
-      </c>
-      <c r="Q76" s="25">
-        <v>190</v>
-      </c>
-      <c r="R76" s="25">
-        <v>186</v>
       </c>
       <c r="S76" s="25"/>
       <c r="T76" s="25"/>
@@ -6304,118 +6332,118 @@
       <c r="AE76" s="25"/>
       <c r="AF76" s="25"/>
     </row>
-    <row r="77" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A77" s="27"/>
       <c r="B77" s="27"/>
       <c r="C77" s="27"/>
-      <c r="D77" s="44" t="s">
+      <c r="D77" s="59" t="s">
         <v>15</v>
       </c>
-      <c r="E77" s="42"/>
-      <c r="F77" s="42"/>
-      <c r="G77" s="43"/>
+      <c r="E77" s="33"/>
+      <c r="F77" s="33"/>
+      <c r="G77" s="34"/>
       <c r="H77" s="28">
-        <f t="shared" ref="H77:AF77" si="3">SUM(H78:H81)</f>
+        <f>SUM(H78:H81)</f>
         <v>0</v>
       </c>
       <c r="I77" s="28">
-        <f t="shared" si="3"/>
+        <f>SUM(I78:I81)</f>
         <v>0</v>
       </c>
       <c r="J77" s="28">
-        <f t="shared" si="3"/>
+        <f>SUM(J78:J81)</f>
         <v>0</v>
       </c>
       <c r="K77" s="28">
-        <f t="shared" si="3"/>
+        <f>SUM(K78:K81)</f>
         <v>0</v>
       </c>
       <c r="L77" s="28">
-        <f t="shared" si="3"/>
+        <f>SUM(L78:L81)</f>
         <v>0</v>
       </c>
       <c r="M77" s="28">
-        <f t="shared" si="3"/>
+        <f>SUM(M78:M81)</f>
         <v>0</v>
       </c>
       <c r="N77" s="28">
-        <f t="shared" si="3"/>
+        <f>SUM(N78:N81)</f>
         <v>0</v>
       </c>
       <c r="O77" s="28">
-        <f t="shared" si="3"/>
+        <f>SUM(O78:O81)</f>
         <v>0</v>
       </c>
       <c r="P77" s="28">
-        <f t="shared" si="3"/>
+        <f>SUM(P78:P81)</f>
         <v>0</v>
       </c>
       <c r="Q77" s="28">
-        <f t="shared" si="3"/>
+        <f>SUM(Q78:Q81)</f>
         <v>0</v>
       </c>
       <c r="R77" s="28">
-        <f t="shared" si="3"/>
+        <f>SUM(R78:R81)</f>
         <v>0</v>
       </c>
       <c r="S77" s="28">
-        <f t="shared" si="3"/>
-        <v>100</v>
+        <f t="shared" ref="H77:AF77" si="3">SUM(S78:S81)</f>
+        <v>81</v>
       </c>
       <c r="T77" s="28">
         <f t="shared" si="3"/>
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="U77" s="28">
         <f t="shared" si="3"/>
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="V77" s="28">
         <f t="shared" si="3"/>
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="W77" s="28">
         <f t="shared" si="3"/>
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="X77" s="28">
         <f t="shared" si="3"/>
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="Y77" s="28">
         <f t="shared" si="3"/>
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="Z77" s="28">
         <f t="shared" si="3"/>
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="AA77" s="28">
         <f t="shared" si="3"/>
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="AB77" s="28">
         <f t="shared" si="3"/>
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="AC77" s="28">
         <f t="shared" si="3"/>
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="AD77" s="28">
         <f t="shared" si="3"/>
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="AE77" s="28">
         <f t="shared" si="3"/>
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="AF77" s="28">
         <f t="shared" si="3"/>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="78" spans="1:32" x14ac:dyDescent="0.25">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="78" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A78" s="1"/>
       <c r="B78" s="1"/>
       <c r="C78" s="1"/>
@@ -6469,62 +6497,62 @@
       </c>
       <c r="S78" s="3">
         <f t="shared" si="4"/>
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="T78" s="3">
         <f t="shared" si="4"/>
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="U78" s="3">
         <f t="shared" si="4"/>
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="V78" s="3">
         <f t="shared" si="4"/>
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="W78" s="3">
         <f t="shared" si="4"/>
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="X78" s="3">
         <f t="shared" si="4"/>
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="Y78" s="3">
         <f t="shared" si="4"/>
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="Z78" s="3">
         <f t="shared" si="4"/>
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="AA78" s="3">
         <f t="shared" si="4"/>
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="AB78" s="3">
         <f t="shared" si="4"/>
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="AC78" s="3">
         <f t="shared" si="4"/>
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="AD78" s="3">
         <f t="shared" si="4"/>
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="AE78" s="3">
         <f t="shared" si="4"/>
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="AF78" s="3">
         <f t="shared" si="4"/>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="79" spans="1:32" x14ac:dyDescent="0.25">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="79" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A79" s="1"/>
       <c r="B79" s="1"/>
       <c r="C79" s="1"/>
@@ -6633,7 +6661,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A80" s="1"/>
       <c r="B80" s="1"/>
       <c r="C80" s="1"/>
@@ -6742,7 +6770,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A81" s="1"/>
       <c r="B81" s="1"/>
       <c r="C81" s="1"/>
@@ -6851,7 +6879,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A82" s="1"/>
       <c r="B82" s="1"/>
       <c r="C82" s="1"/>
@@ -6885,7 +6913,7 @@
       <c r="AE82" s="1"/>
       <c r="AF82" s="1"/>
     </row>
-    <row r="83" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A83" s="1"/>
       <c r="B83" s="1"/>
       <c r="C83" s="1"/>
@@ -6919,7 +6947,7 @@
       <c r="AE83" s="1"/>
       <c r="AF83" s="1"/>
     </row>
-    <row r="84" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A84" s="1"/>
       <c r="B84" s="1"/>
       <c r="C84" s="1"/>
@@ -6953,7 +6981,7 @@
       <c r="AE84" s="1"/>
       <c r="AF84" s="1"/>
     </row>
-    <row r="85" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A85" s="1"/>
       <c r="B85" s="1"/>
       <c r="C85" s="1"/>
@@ -6987,7 +7015,7 @@
       <c r="AE85" s="1"/>
       <c r="AF85" s="1"/>
     </row>
-    <row r="86" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A86" s="1"/>
       <c r="B86" s="1"/>
       <c r="C86" s="1"/>
@@ -7021,7 +7049,7 @@
       <c r="AE86" s="1"/>
       <c r="AF86" s="1"/>
     </row>
-    <row r="87" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A87" s="1"/>
       <c r="B87" s="1"/>
       <c r="C87" s="1"/>
@@ -7055,7 +7083,7 @@
       <c r="AE87" s="1"/>
       <c r="AF87" s="1"/>
     </row>
-    <row r="88" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A88" s="1"/>
       <c r="B88" s="1"/>
       <c r="C88" s="1"/>
@@ -7089,7 +7117,7 @@
       <c r="AE88" s="1"/>
       <c r="AF88" s="1"/>
     </row>
-    <row r="89" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A89" s="1"/>
       <c r="B89" s="1"/>
       <c r="C89" s="1"/>
@@ -7123,7 +7151,7 @@
       <c r="AE89" s="1"/>
       <c r="AF89" s="1"/>
     </row>
-    <row r="90" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A90" s="1"/>
       <c r="B90" s="1"/>
       <c r="C90" s="1"/>
@@ -7157,7 +7185,7 @@
       <c r="AE90" s="1"/>
       <c r="AF90" s="1"/>
     </row>
-    <row r="91" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A91" s="1"/>
       <c r="B91" s="1"/>
       <c r="C91" s="1"/>
@@ -7191,7 +7219,7 @@
       <c r="AE91" s="1"/>
       <c r="AF91" s="1"/>
     </row>
-    <row r="92" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A92" s="1"/>
       <c r="B92" s="1"/>
       <c r="C92" s="1"/>
@@ -7225,7 +7253,7 @@
       <c r="AE92" s="1"/>
       <c r="AF92" s="1"/>
     </row>
-    <row r="93" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A93" s="1"/>
       <c r="B93" s="1"/>
       <c r="C93" s="1"/>
@@ -7259,7 +7287,7 @@
       <c r="AE93" s="1"/>
       <c r="AF93" s="1"/>
     </row>
-    <row r="94" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A94" s="1"/>
       <c r="B94" s="1"/>
       <c r="C94" s="1"/>
@@ -7293,7 +7321,7 @@
       <c r="AE94" s="1"/>
       <c r="AF94" s="1"/>
     </row>
-    <row r="95" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A95" s="1"/>
       <c r="B95" s="1"/>
       <c r="C95" s="1"/>
@@ -7327,7 +7355,7 @@
       <c r="AE95" s="1"/>
       <c r="AF95" s="1"/>
     </row>
-    <row r="96" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A96" s="1"/>
       <c r="B96" s="1"/>
       <c r="C96" s="1"/>
@@ -7361,7 +7389,7 @@
       <c r="AE96" s="1"/>
       <c r="AF96" s="1"/>
     </row>
-    <row r="97" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A97" s="1"/>
       <c r="B97" s="1"/>
       <c r="C97" s="1"/>
@@ -7395,7 +7423,7 @@
       <c r="AE97" s="1"/>
       <c r="AF97" s="1"/>
     </row>
-    <row r="98" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A98" s="1"/>
       <c r="B98" s="1"/>
       <c r="C98" s="1"/>
@@ -7429,7 +7457,7 @@
       <c r="AE98" s="1"/>
       <c r="AF98" s="1"/>
     </row>
-    <row r="99" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A99" s="1"/>
       <c r="B99" s="1"/>
       <c r="C99" s="1"/>
@@ -7463,7 +7491,7 @@
       <c r="AE99" s="1"/>
       <c r="AF99" s="1"/>
     </row>
-    <row r="100" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A100" s="1"/>
       <c r="B100" s="1"/>
       <c r="C100" s="1"/>
@@ -7497,7 +7525,7 @@
       <c r="AE100" s="1"/>
       <c r="AF100" s="1"/>
     </row>
-    <row r="101" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="1"/>
       <c r="B101" s="1"/>
       <c r="C101" s="1"/>
@@ -7506,7 +7534,7 @@
       <c r="F101" s="1"/>
       <c r="G101" s="1"/>
     </row>
-    <row r="102" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="1"/>
       <c r="B102" s="1"/>
       <c r="C102" s="1"/>
@@ -7515,7 +7543,7 @@
       <c r="F102" s="1"/>
       <c r="G102" s="1"/>
     </row>
-    <row r="103" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="1"/>
       <c r="B103" s="1"/>
       <c r="C103" s="1"/>
@@ -7524,7 +7552,7 @@
       <c r="F103" s="1"/>
       <c r="G103" s="1"/>
     </row>
-    <row r="104" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="1"/>
       <c r="B104" s="1"/>
       <c r="C104" s="1"/>
@@ -7533,7 +7561,7 @@
       <c r="F104" s="1"/>
       <c r="G104" s="1"/>
     </row>
-    <row r="105" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="1"/>
       <c r="B105" s="1"/>
       <c r="C105" s="1"/>
@@ -7542,7 +7570,7 @@
       <c r="F105" s="1"/>
       <c r="G105" s="1"/>
     </row>
-    <row r="106" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="1"/>
       <c r="B106" s="1"/>
       <c r="C106" s="1"/>
@@ -7551,7 +7579,7 @@
       <c r="F106" s="1"/>
       <c r="G106" s="1"/>
     </row>
-    <row r="107" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="1"/>
       <c r="B107" s="1"/>
       <c r="C107" s="1"/>
@@ -7560,7 +7588,7 @@
       <c r="F107" s="1"/>
       <c r="G107" s="1"/>
     </row>
-    <row r="108" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="1"/>
       <c r="B108" s="1"/>
       <c r="C108" s="1"/>
@@ -7569,7 +7597,7 @@
       <c r="F108" s="1"/>
       <c r="G108" s="1"/>
     </row>
-    <row r="109" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="1"/>
       <c r="B109" s="1"/>
       <c r="C109" s="1"/>
@@ -7578,7 +7606,7 @@
       <c r="F109" s="1"/>
       <c r="G109" s="1"/>
     </row>
-    <row r="110" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="1"/>
       <c r="B110" s="1"/>
       <c r="C110" s="1"/>
@@ -7587,7 +7615,7 @@
       <c r="F110" s="1"/>
       <c r="G110" s="1"/>
     </row>
-    <row r="111" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="1"/>
       <c r="B111" s="1"/>
       <c r="C111" s="1"/>
@@ -7596,7 +7624,7 @@
       <c r="F111" s="1"/>
       <c r="G111" s="1"/>
     </row>
-    <row r="112" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="1"/>
       <c r="B112" s="1"/>
       <c r="C112" s="1"/>
@@ -7605,7 +7633,7 @@
       <c r="F112" s="1"/>
       <c r="G112" s="1"/>
     </row>
-    <row r="113" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="1"/>
       <c r="B113" s="1"/>
       <c r="C113" s="1"/>
@@ -7614,7 +7642,7 @@
       <c r="F113" s="1"/>
       <c r="G113" s="1"/>
     </row>
-    <row r="114" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="1"/>
       <c r="B114" s="1"/>
       <c r="C114" s="1"/>
@@ -7623,7 +7651,7 @@
       <c r="F114" s="1"/>
       <c r="G114" s="1"/>
     </row>
-    <row r="115" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="1"/>
       <c r="B115" s="1"/>
       <c r="C115" s="1"/>
@@ -7632,7 +7660,7 @@
       <c r="F115" s="1"/>
       <c r="G115" s="1"/>
     </row>
-    <row r="116" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="1"/>
       <c r="B116" s="1"/>
       <c r="C116" s="1"/>
@@ -7641,7 +7669,7 @@
       <c r="F116" s="1"/>
       <c r="G116" s="1"/>
     </row>
-    <row r="117" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="1"/>
       <c r="B117" s="1"/>
       <c r="C117" s="1"/>
@@ -7650,7 +7678,7 @@
       <c r="F117" s="1"/>
       <c r="G117" s="1"/>
     </row>
-    <row r="118" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="1"/>
       <c r="B118" s="1"/>
       <c r="C118" s="1"/>
@@ -7659,7 +7687,7 @@
       <c r="F118" s="1"/>
       <c r="G118" s="1"/>
     </row>
-    <row r="119" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="1"/>
       <c r="B119" s="1"/>
       <c r="C119" s="1"/>
@@ -7668,7 +7696,7 @@
       <c r="F119" s="1"/>
       <c r="G119" s="1"/>
     </row>
-    <row r="120" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="1"/>
       <c r="B120" s="1"/>
       <c r="C120" s="1"/>
@@ -7677,7 +7705,7 @@
       <c r="F120" s="1"/>
       <c r="G120" s="1"/>
     </row>
-    <row r="121" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="1"/>
       <c r="B121" s="1"/>
       <c r="C121" s="1"/>
@@ -7686,7 +7714,7 @@
       <c r="F121" s="1"/>
       <c r="G121" s="1"/>
     </row>
-    <row r="122" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="1"/>
       <c r="B122" s="1"/>
       <c r="C122" s="1"/>
@@ -7695,7 +7723,7 @@
       <c r="F122" s="1"/>
       <c r="G122" s="1"/>
     </row>
-    <row r="123" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="1"/>
       <c r="B123" s="1"/>
       <c r="C123" s="1"/>
@@ -7704,7 +7732,7 @@
       <c r="F123" s="1"/>
       <c r="G123" s="1"/>
     </row>
-    <row r="124" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" s="1"/>
       <c r="B124" s="1"/>
       <c r="C124" s="1"/>
@@ -7714,7 +7742,18 @@
       <c r="G124" s="1"/>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" columnSort="1" ref="H2:R77">
+    <sortCondition descending="1" ref="H3:R3"/>
+    <sortCondition descending="1" ref="H77:R77"/>
+  </sortState>
   <mergeCells count="18">
+    <mergeCell ref="A64:A69"/>
+    <mergeCell ref="A70:A75"/>
+    <mergeCell ref="A46:A51"/>
+    <mergeCell ref="D76:F76"/>
+    <mergeCell ref="D77:G77"/>
+    <mergeCell ref="A52:A57"/>
+    <mergeCell ref="A58:A63"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="E3:F3"/>
     <mergeCell ref="A4:A9"/>
@@ -7726,13 +7765,6 @@
     <mergeCell ref="A16:A21"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="D2:G2"/>
-    <mergeCell ref="A64:A69"/>
-    <mergeCell ref="A70:A75"/>
-    <mergeCell ref="A46:A51"/>
-    <mergeCell ref="D76:F76"/>
-    <mergeCell ref="D77:G77"/>
-    <mergeCell ref="A52:A57"/>
-    <mergeCell ref="A58:A63"/>
   </mergeCells>
   <conditionalFormatting sqref="H3:AF3">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
@@ -7747,14 +7779,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:O100"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="6" width="11.42578125" customWidth="1"/>
-    <col min="7" max="7" width="16.85546875" customWidth="1"/>
-    <col min="8" max="15" width="11.42578125" customWidth="1"/>
+    <col min="1" max="6" width="11.44140625" customWidth="1"/>
+    <col min="7" max="7" width="16.88671875" customWidth="1"/>
+    <col min="8" max="15" width="11.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="4"/>
       <c r="B1" s="4" t="s">
         <v>16</v>
@@ -7801,7 +7833,7 @@
         <v>SI(G28-H28=-2;98;</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4"/>
       <c r="B2" s="4" t="s">
         <v>16</v>
@@ -7846,7 +7878,7 @@
         <v>SI(G28-H28=-3;97;</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4"/>
       <c r="B3" s="4" t="s">
         <v>16</v>
@@ -7891,7 +7923,7 @@
         <v>SI(G28-H28=-4;96;</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4"/>
       <c r="B4" s="4" t="s">
         <v>16</v>
@@ -7936,7 +7968,7 @@
         <v>SI(G28-H28=-5;95;</v>
       </c>
     </row>
-    <row r="5" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4"/>
       <c r="B5" s="4" t="s">
         <v>16</v>
@@ -7981,7 +8013,7 @@
         <v>SI(G28-H28=-6;94;</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="4"/>
       <c r="B6" s="4" t="s">
         <v>16</v>
@@ -8026,7 +8058,7 @@
         <v>SI(G28-H28=-7;93;</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4"/>
       <c r="B7" s="4" t="s">
         <v>16</v>
@@ -8071,7 +8103,7 @@
         <v>SI(G28-H28=-8;92;</v>
       </c>
     </row>
-    <row r="8" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4"/>
       <c r="B8" s="4" t="s">
         <v>16</v>
@@ -8116,7 +8148,7 @@
         <v>SI(G28-H28=-9;91;</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4"/>
       <c r="B9" s="4" t="s">
         <v>16</v>
@@ -8161,7 +8193,7 @@
         <v>SI(G28-H28=-10;90;</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4"/>
       <c r="B10" s="4" t="s">
         <v>16</v>
@@ -8206,7 +8238,7 @@
         <v>SI(G28-H28=-11;89;</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4"/>
       <c r="B11" s="4" t="s">
         <v>16</v>
@@ -8251,7 +8283,7 @@
         <v>SI(G28-H28=-12;88;</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4"/>
       <c r="B12" s="4" t="s">
         <v>16</v>
@@ -8296,7 +8328,7 @@
         <v>SI(G28-H28=-13;87;</v>
       </c>
     </row>
-    <row r="13" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="4"/>
       <c r="B13" s="4" t="s">
         <v>16</v>
@@ -8341,7 +8373,7 @@
         <v>SI(G28-H28=-14;86;</v>
       </c>
     </row>
-    <row r="14" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="4"/>
       <c r="B14" s="4" t="s">
         <v>16</v>
@@ -8386,7 +8418,7 @@
         <v>SI(G28-H28=-15;85;</v>
       </c>
     </row>
-    <row r="15" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="4"/>
       <c r="B15" s="4" t="s">
         <v>16</v>
@@ -8431,7 +8463,7 @@
         <v>SI(G28-H28=-16;84;</v>
       </c>
     </row>
-    <row r="16" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="4"/>
       <c r="B16" s="4" t="s">
         <v>16</v>
@@ -8476,7 +8508,7 @@
         <v>SI(G28-H28=-17;83;</v>
       </c>
     </row>
-    <row r="17" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4"/>
       <c r="B17" s="4" t="s">
         <v>16</v>
@@ -8521,7 +8553,7 @@
         <v>SI(G28-H28=-18;82;</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A18" s="4"/>
       <c r="B18" s="4" t="s">
         <v>16</v>
@@ -8566,7 +8598,7 @@
         <v>SI(G28-H28=-19;81;</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A19" s="4"/>
       <c r="B19" s="4" t="s">
         <v>16</v>
@@ -8611,7 +8643,7 @@
         <v>SI(G28-H28=-20;80;</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A20" s="4"/>
       <c r="B20" s="4" t="s">
         <v>16</v>
@@ -8656,7 +8688,7 @@
         <v>SI(G28-H28=-21;79;</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A21" s="4"/>
       <c r="B21" s="4" t="s">
         <v>16</v>
@@ -8701,7 +8733,7 @@
         <v>SI(G28-H28=-22;78;</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A22" s="4"/>
       <c r="B22" s="4" t="s">
         <v>16</v>
@@ -8746,7 +8778,7 @@
         <v>SI(G28-H28=-23;77;</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A23" s="4"/>
       <c r="B23" s="4" t="s">
         <v>16</v>
@@ -8791,7 +8823,7 @@
         <v>SI(G28-H28=-24;76;</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A24" s="4"/>
       <c r="B24" s="4" t="s">
         <v>16</v>
@@ -8836,7 +8868,7 @@
         <v>SI(G28-H28=-25;75;</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A25" s="4"/>
       <c r="B25" s="4" t="s">
         <v>16</v>
@@ -8881,7 +8913,7 @@
         <v>SI(G28-H28=-26;74;</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A26" s="4"/>
       <c r="B26" s="4" t="s">
         <v>16</v>
@@ -8926,7 +8958,7 @@
         <v>SI(G28-H28=-27;73;</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A27" s="4"/>
       <c r="B27" s="4" t="s">
         <v>16</v>
@@ -8971,7 +9003,7 @@
         <v>SI(G28-H28=-28;72;</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A28" s="4"/>
       <c r="B28" s="4" t="s">
         <v>16</v>
@@ -9016,7 +9048,7 @@
         <v>SI(G28-H28=-29;71;</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A29" s="4"/>
       <c r="B29" s="4" t="s">
         <v>16</v>
@@ -9061,7 +9093,7 @@
         <v>SI(G28-H28=-30;70;</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A30" s="4"/>
       <c r="B30" s="4" t="s">
         <v>16</v>
@@ -9106,7 +9138,7 @@
         <v>SI(G28-H28=-31;69;</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A31" s="4"/>
       <c r="B31" s="4" t="s">
         <v>16</v>
@@ -9151,7 +9183,7 @@
         <v>SI(G28-H28=-32;68;</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A32" s="4"/>
       <c r="B32" s="4" t="s">
         <v>16</v>
@@ -9196,7 +9228,7 @@
         <v>SI(G28-H28=-33;67;</v>
       </c>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A33" s="4"/>
       <c r="B33" s="4" t="s">
         <v>16</v>
@@ -9241,7 +9273,7 @@
         <v>SI(G28-H28=-34;66;</v>
       </c>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A34" s="4"/>
       <c r="B34" s="4" t="s">
         <v>16</v>
@@ -9286,7 +9318,7 @@
         <v>SI(G28-H28=-35;65;</v>
       </c>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A35" s="4"/>
       <c r="B35" s="4" t="s">
         <v>16</v>
@@ -9331,7 +9363,7 @@
         <v>SI(G28-H28=-36;64;</v>
       </c>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A36" s="4"/>
       <c r="B36" s="4" t="s">
         <v>16</v>
@@ -9376,7 +9408,7 @@
         <v>SI(G28-H28=-37;63;</v>
       </c>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A37" s="4"/>
       <c r="B37" s="4" t="s">
         <v>16</v>
@@ -9421,7 +9453,7 @@
         <v>SI(G28-H28=-38;62;</v>
       </c>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A38" s="4"/>
       <c r="B38" s="4" t="s">
         <v>16</v>
@@ -9466,7 +9498,7 @@
         <v>SI(G28-H28=-39;61;</v>
       </c>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A39" s="4"/>
       <c r="B39" s="4" t="s">
         <v>16</v>
@@ -9511,7 +9543,7 @@
         <v>SI(G28-H28=-40;60;</v>
       </c>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A40" s="4"/>
       <c r="B40" s="4" t="s">
         <v>16</v>
@@ -9556,7 +9588,7 @@
         <v>SI(G28-H28=-41;59;</v>
       </c>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A41" s="4"/>
       <c r="B41" s="4" t="s">
         <v>16</v>
@@ -9601,7 +9633,7 @@
         <v>SI(G28-H28=-42;58;</v>
       </c>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="4"/>
       <c r="B42" s="4" t="s">
         <v>16</v>
@@ -9646,7 +9678,7 @@
         <v>SI(G28-H28=-43;57;</v>
       </c>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A43" s="4"/>
       <c r="B43" s="4" t="s">
         <v>16</v>
@@ -9691,7 +9723,7 @@
         <v>SI(G28-H28=-44;56;</v>
       </c>
     </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A44" s="4"/>
       <c r="B44" s="4" t="s">
         <v>16</v>
@@ -9736,7 +9768,7 @@
         <v>SI(G28-H28=-45;55;</v>
       </c>
     </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A45" s="4"/>
       <c r="B45" s="4" t="s">
         <v>16</v>
@@ -9781,7 +9813,7 @@
         <v>SI(G28-H28=-46;54;</v>
       </c>
     </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A46" s="4"/>
       <c r="B46" s="4" t="s">
         <v>16</v>
@@ -9826,7 +9858,7 @@
         <v>SI(G28-H28=-47;53;</v>
       </c>
     </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A47" s="4"/>
       <c r="B47" s="4" t="s">
         <v>16</v>
@@ -9871,7 +9903,7 @@
         <v>SI(G28-H28=-48;52;</v>
       </c>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A48" s="4"/>
       <c r="B48" s="4" t="s">
         <v>16</v>
@@ -9916,7 +9948,7 @@
         <v>SI(G28-H28=-49;51;</v>
       </c>
     </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A49" s="4"/>
       <c r="B49" s="4" t="s">
         <v>16</v>
@@ -9961,7 +9993,7 @@
         <v>SI(G28-H28=-50;50;</v>
       </c>
     </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A50" s="4"/>
       <c r="B50" s="4" t="s">
         <v>16</v>
@@ -10006,7 +10038,7 @@
         <v>SI(G28-H28=-51;49;</v>
       </c>
     </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A51" s="4"/>
       <c r="B51" s="4" t="s">
         <v>16</v>
@@ -10051,7 +10083,7 @@
         <v>SI(G28-H28=-52;48;</v>
       </c>
     </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A52" s="4"/>
       <c r="B52" s="4" t="s">
         <v>16</v>
@@ -10096,7 +10128,7 @@
         <v>SI(G28-H28=-53;47;</v>
       </c>
     </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A53" s="4"/>
       <c r="B53" s="4" t="s">
         <v>16</v>
@@ -10141,7 +10173,7 @@
         <v>SI(G28-H28=-54;46;</v>
       </c>
     </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A54" s="4"/>
       <c r="B54" s="4" t="s">
         <v>16</v>
@@ -10186,7 +10218,7 @@
         <v>SI(G28-H28=-55;45;</v>
       </c>
     </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A55" s="4"/>
       <c r="B55" s="4" t="s">
         <v>16</v>
@@ -10231,7 +10263,7 @@
         <v>SI(G28-H28=-56;44;</v>
       </c>
     </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A56" s="4"/>
       <c r="B56" s="4" t="s">
         <v>16</v>
@@ -10276,7 +10308,7 @@
         <v>SI(G28-H28=-57;43;</v>
       </c>
     </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A57" s="4"/>
       <c r="B57" s="4" t="s">
         <v>16</v>
@@ -10321,7 +10353,7 @@
         <v>SI(G28-H28=-58;42;</v>
       </c>
     </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A58" s="4"/>
       <c r="B58" s="4" t="s">
         <v>16</v>
@@ -10366,7 +10398,7 @@
         <v>SI(G28-H28=-59;41;</v>
       </c>
     </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A59" s="4"/>
       <c r="B59" s="4" t="s">
         <v>16</v>
@@ -10411,7 +10443,7 @@
         <v>SI(G28-H28=-60;40;</v>
       </c>
     </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A60" s="4"/>
       <c r="B60" s="4" t="s">
         <v>16</v>
@@ -10456,7 +10488,7 @@
         <v>SI(G28-H28=-61;39;</v>
       </c>
     </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A61" s="4"/>
       <c r="B61" s="4" t="s">
         <v>16</v>
@@ -10501,7 +10533,7 @@
         <v>SI(G28-H28=-62;38;</v>
       </c>
     </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A62" s="4"/>
       <c r="B62" s="4" t="s">
         <v>16</v>
@@ -10546,7 +10578,7 @@
         <v>SI(G28-H28=-63;37;</v>
       </c>
     </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A63" s="4"/>
       <c r="B63" s="4" t="s">
         <v>16</v>
@@ -10591,7 +10623,7 @@
         <v>SI(G28-H28=-64;36;</v>
       </c>
     </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A64" s="4"/>
       <c r="B64" s="4" t="s">
         <v>16</v>
@@ -10636,7 +10668,7 @@
         <v>SI(G28-H28=-65;35;</v>
       </c>
     </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A65" s="4"/>
       <c r="B65" s="4" t="s">
         <v>16</v>
@@ -10681,7 +10713,7 @@
         <v>SI(G28-H28=-66;34;</v>
       </c>
     </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A66" s="4"/>
       <c r="B66" s="4" t="s">
         <v>16</v>
@@ -10726,7 +10758,7 @@
         <v>SI(G28-H28=-67;33;</v>
       </c>
     </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A67" s="4"/>
       <c r="B67" s="4" t="s">
         <v>16</v>
@@ -10771,7 +10803,7 @@
         <v>SI(G28-H28=-68;32;</v>
       </c>
     </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A68" s="4"/>
       <c r="B68" s="4" t="s">
         <v>16</v>
@@ -10816,7 +10848,7 @@
         <v>SI(G28-H28=-69;31;</v>
       </c>
     </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A69" s="4"/>
       <c r="B69" s="4" t="s">
         <v>16</v>
@@ -10861,7 +10893,7 @@
         <v>SI(G28-H28=-70;30;</v>
       </c>
     </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A70" s="4"/>
       <c r="B70" s="4" t="s">
         <v>16</v>
@@ -10906,7 +10938,7 @@
         <v>SI(G28-H28=-71;29;</v>
       </c>
     </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A71" s="4"/>
       <c r="B71" s="4" t="s">
         <v>16</v>
@@ -10951,7 +10983,7 @@
         <v>SI(G28-H28=-72;28;</v>
       </c>
     </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A72" s="4"/>
       <c r="B72" s="4" t="s">
         <v>16</v>
@@ -10996,7 +11028,7 @@
         <v>SI(G28-H28=-73;27;</v>
       </c>
     </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A73" s="4"/>
       <c r="B73" s="4" t="s">
         <v>16</v>
@@ -11041,7 +11073,7 @@
         <v>SI(G28-H28=-74;26;</v>
       </c>
     </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A74" s="4"/>
       <c r="B74" s="4" t="s">
         <v>16</v>
@@ -11086,7 +11118,7 @@
         <v>SI(G28-H28=-75;25;</v>
       </c>
     </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A75" s="4"/>
       <c r="B75" s="4" t="s">
         <v>16</v>
@@ -11131,7 +11163,7 @@
         <v>SI(G28-H28=-76;24;</v>
       </c>
     </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A76" s="4"/>
       <c r="B76" s="4" t="s">
         <v>16</v>
@@ -11176,7 +11208,7 @@
         <v>SI(G28-H28=-77;23;</v>
       </c>
     </row>
-    <row r="77" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A77" s="4"/>
       <c r="B77" s="4" t="s">
         <v>16</v>
@@ -11221,7 +11253,7 @@
         <v>SI(G28-H28=-78;22;</v>
       </c>
     </row>
-    <row r="78" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A78" s="4"/>
       <c r="B78" s="4" t="s">
         <v>16</v>
@@ -11266,7 +11298,7 @@
         <v>SI(G28-H28=-79;21;</v>
       </c>
     </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A79" s="4"/>
       <c r="B79" s="4" t="s">
         <v>16</v>
@@ -11311,7 +11343,7 @@
         <v>SI(G28-H28=-80;20;</v>
       </c>
     </row>
-    <row r="80" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A80" s="4"/>
       <c r="B80" s="4" t="s">
         <v>16</v>
@@ -11356,7 +11388,7 @@
         <v>SI(G28-H28=-81;19;</v>
       </c>
     </row>
-    <row r="81" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A81" s="4"/>
       <c r="B81" s="4" t="s">
         <v>16</v>
@@ -11401,7 +11433,7 @@
         <v>SI(G28-H28=-82;18;</v>
       </c>
     </row>
-    <row r="82" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A82" s="4"/>
       <c r="B82" s="4" t="s">
         <v>16</v>
@@ -11446,7 +11478,7 @@
         <v>SI(G28-H28=-83;17;</v>
       </c>
     </row>
-    <row r="83" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A83" s="4"/>
       <c r="B83" s="4" t="s">
         <v>16</v>
@@ -11491,7 +11523,7 @@
         <v>SI(G28-H28=-84;16;</v>
       </c>
     </row>
-    <row r="84" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A84" s="4"/>
       <c r="B84" s="4" t="s">
         <v>16</v>
@@ -11536,7 +11568,7 @@
         <v>SI(G28-H28=-85;15;</v>
       </c>
     </row>
-    <row r="85" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A85" s="4"/>
       <c r="B85" s="4" t="s">
         <v>16</v>
@@ -11581,7 +11613,7 @@
         <v>SI(G28-H28=-86;14;</v>
       </c>
     </row>
-    <row r="86" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A86" s="4"/>
       <c r="B86" s="4" t="s">
         <v>16</v>
@@ -11626,7 +11658,7 @@
         <v>SI(G28-H28=-87;13;</v>
       </c>
     </row>
-    <row r="87" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A87" s="4"/>
       <c r="B87" s="4" t="s">
         <v>16</v>
@@ -11671,7 +11703,7 @@
         <v>SI(G28-H28=-88;12;</v>
       </c>
     </row>
-    <row r="88" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A88" s="4"/>
       <c r="B88" s="4" t="s">
         <v>16</v>
@@ -11716,7 +11748,7 @@
         <v>SI(G28-H28=-89;11;</v>
       </c>
     </row>
-    <row r="89" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A89" s="4"/>
       <c r="B89" s="4" t="s">
         <v>16</v>
@@ -11761,7 +11793,7 @@
         <v>SI(G28-H28=-90;10;</v>
       </c>
     </row>
-    <row r="90" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A90" s="4"/>
       <c r="B90" s="4" t="s">
         <v>16</v>
@@ -11806,7 +11838,7 @@
         <v>SI(G28-H28=-91;9;</v>
       </c>
     </row>
-    <row r="91" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A91" s="4"/>
       <c r="B91" s="4" t="s">
         <v>16</v>
@@ -11851,7 +11883,7 @@
         <v>SI(G28-H28=-92;8;</v>
       </c>
     </row>
-    <row r="92" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A92" s="4"/>
       <c r="B92" s="4" t="s">
         <v>16</v>
@@ -11896,7 +11928,7 @@
         <v>SI(G28-H28=-93;7;</v>
       </c>
     </row>
-    <row r="93" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A93" s="4"/>
       <c r="B93" s="4" t="s">
         <v>16</v>
@@ -11941,7 +11973,7 @@
         <v>SI(G28-H28=-94;6;</v>
       </c>
     </row>
-    <row r="94" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A94" s="4"/>
       <c r="B94" s="4" t="s">
         <v>16</v>
@@ -11986,7 +12018,7 @@
         <v>SI(G28-H28=-95;5;</v>
       </c>
     </row>
-    <row r="95" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A95" s="4"/>
       <c r="B95" s="4" t="s">
         <v>16</v>
@@ -12031,7 +12063,7 @@
         <v>SI(G28-H28=-96;4;</v>
       </c>
     </row>
-    <row r="96" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A96" s="4"/>
       <c r="B96" s="4" t="s">
         <v>16</v>
@@ -12076,7 +12108,7 @@
         <v>SI(G28-H28=-97;3;</v>
       </c>
     </row>
-    <row r="97" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A97" s="4"/>
       <c r="B97" s="4" t="s">
         <v>16</v>
@@ -12121,7 +12153,7 @@
         <v>SI(G28-H28=-98;2;</v>
       </c>
     </row>
-    <row r="98" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A98" s="4"/>
       <c r="B98" s="4" t="s">
         <v>16</v>
@@ -12166,7 +12198,7 @@
         <v>SI(G28-H28=-99;1;</v>
       </c>
     </row>
-    <row r="99" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A99" s="4"/>
       <c r="B99" s="4" t="s">
         <v>16</v>
@@ -12211,7 +12243,7 @@
         <v>SI(G28-H28=-100;0;</v>
       </c>
     </row>
-    <row r="100" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A100" s="4"/>
       <c r="B100" s="4"/>
       <c r="C100" s="4"/>
@@ -12237,9 +12269,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="11" width="10.7109375" customWidth="1"/>
+    <col min="1" max="11" width="10.6640625" customWidth="1"/>
   </cols>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -12250,26 +12282,26 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:B100"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="29.85546875" customWidth="1"/>
-    <col min="2" max="6" width="11.42578125" customWidth="1"/>
-    <col min="7" max="11" width="10.7109375" customWidth="1"/>
+    <col min="1" max="1" width="29.88671875" customWidth="1"/>
+    <col min="2" max="6" width="11.44140625" customWidth="1"/>
+    <col min="7" max="11" width="10.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>20</v>
       </c>
       <c r="B1" s="1"/>
     </row>
-    <row r="2" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
         <v>21</v>
       </c>
       <c r="B2" s="1"/>
     </row>
-    <row r="3" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>22</v>
       </c>
@@ -12277,61 +12309,61 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>24</v>
       </c>
       <c r="B4" s="1"/>
     </row>
-    <row r="5" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>25</v>
       </c>
       <c r="B5" s="1"/>
     </row>
-    <row r="6" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
         <v>26</v>
       </c>
       <c r="B6" s="1"/>
     </row>
-    <row r="7" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>27</v>
       </c>
       <c r="B7" s="1"/>
     </row>
-    <row r="8" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
         <v>28</v>
       </c>
       <c r="B8" s="1"/>
     </row>
-    <row r="9" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
         <v>29</v>
       </c>
       <c r="B9" s="1"/>
     </row>
-    <row r="10" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
         <v>30</v>
       </c>
       <c r="B10" s="1"/>
     </row>
-    <row r="11" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
         <v>31</v>
       </c>
       <c r="B11" s="1"/>
     </row>
-    <row r="12" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
         <v>32</v>
       </c>
       <c r="B12" s="1"/>
     </row>
-    <row r="13" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
         <v>33</v>
       </c>
@@ -12339,7 +12371,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
         <v>34</v>
       </c>
@@ -12347,19 +12379,19 @@
         <v>23</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
         <v>35</v>
       </c>
       <c r="B15" s="1"/>
     </row>
-    <row r="16" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
         <v>36</v>
       </c>
       <c r="B16" s="1"/>
     </row>
-    <row r="17" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
         <v>37</v>
       </c>
@@ -12367,19 +12399,19 @@
         <v>23</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
         <v>38</v>
       </c>
       <c r="B18" s="1"/>
     </row>
-    <row r="19" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
         <v>39</v>
       </c>
       <c r="B19" s="1"/>
     </row>
-    <row r="20" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
         <v>40</v>
       </c>
@@ -12387,19 +12419,19 @@
         <v>23</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
         <v>41</v>
       </c>
       <c r="B21" s="5"/>
     </row>
-    <row r="22" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
         <v>42</v>
       </c>
       <c r="B22" s="1"/>
     </row>
-    <row r="23" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
         <v>43</v>
       </c>
@@ -12407,13 +12439,13 @@
         <v>23</v>
       </c>
     </row>
-    <row r="24" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
         <v>44</v>
       </c>
       <c r="B24" s="1"/>
     </row>
-    <row r="25" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
         <v>45</v>
       </c>
@@ -12421,229 +12453,229 @@
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B26" s="1"/>
     </row>
-    <row r="27" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B27" s="1"/>
     </row>
-    <row r="28" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B28" s="1"/>
     </row>
-    <row r="29" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B29" s="1"/>
     </row>
-    <row r="30" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B30" s="1"/>
     </row>
-    <row r="31" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B31" s="1"/>
     </row>
-    <row r="32" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B32" s="1"/>
     </row>
-    <row r="33" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B33" s="1"/>
     </row>
-    <row r="34" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B34" s="1"/>
     </row>
-    <row r="35" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B35" s="1"/>
     </row>
-    <row r="36" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B36" s="1"/>
     </row>
-    <row r="37" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B37" s="1"/>
     </row>
-    <row r="38" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B38" s="1"/>
     </row>
-    <row r="39" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B39" s="1"/>
     </row>
-    <row r="40" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B40" s="1"/>
     </row>
-    <row r="41" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B41" s="1"/>
     </row>
-    <row r="42" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B42" s="1"/>
     </row>
-    <row r="43" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B43" s="1"/>
     </row>
-    <row r="44" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B44" s="1"/>
     </row>
-    <row r="45" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B45" s="1"/>
     </row>
-    <row r="46" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B46" s="1"/>
     </row>
-    <row r="47" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B47" s="1"/>
     </row>
-    <row r="48" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B48" s="1"/>
     </row>
-    <row r="49" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B49" s="1"/>
     </row>
-    <row r="50" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B50" s="1"/>
     </row>
-    <row r="51" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B51" s="1"/>
     </row>
-    <row r="52" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B52" s="1"/>
     </row>
-    <row r="53" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B53" s="1"/>
     </row>
-    <row r="54" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B54" s="1"/>
     </row>
-    <row r="55" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B55" s="1"/>
     </row>
-    <row r="56" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B56" s="1"/>
     </row>
-    <row r="57" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B57" s="1"/>
     </row>
-    <row r="58" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B58" s="1"/>
     </row>
-    <row r="59" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B59" s="1"/>
     </row>
-    <row r="60" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B60" s="1"/>
     </row>
-    <row r="61" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B61" s="1"/>
     </row>
-    <row r="62" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B62" s="1"/>
     </row>
-    <row r="63" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B63" s="1"/>
     </row>
-    <row r="64" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B64" s="1"/>
     </row>
-    <row r="65" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B65" s="1"/>
     </row>
-    <row r="66" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B66" s="1"/>
     </row>
-    <row r="67" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B67" s="1"/>
     </row>
-    <row r="68" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B68" s="1"/>
     </row>
-    <row r="69" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B69" s="1"/>
     </row>
-    <row r="70" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B70" s="1"/>
     </row>
-    <row r="71" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B71" s="1"/>
     </row>
-    <row r="72" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B72" s="1"/>
     </row>
-    <row r="73" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B73" s="1"/>
     </row>
-    <row r="74" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B74" s="1"/>
     </row>
-    <row r="75" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B75" s="1"/>
     </row>
-    <row r="76" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B76" s="1"/>
     </row>
-    <row r="77" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B77" s="1"/>
     </row>
-    <row r="78" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B78" s="1"/>
     </row>
-    <row r="79" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B79" s="1"/>
     </row>
-    <row r="80" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B80" s="1"/>
     </row>
-    <row r="81" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B81" s="1"/>
     </row>
-    <row r="82" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B82" s="1"/>
     </row>
-    <row r="83" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B83" s="1"/>
     </row>
-    <row r="84" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B84" s="1"/>
     </row>
-    <row r="85" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B85" s="1"/>
     </row>
-    <row r="86" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B86" s="1"/>
     </row>
-    <row r="87" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B87" s="1"/>
     </row>
-    <row r="88" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B88" s="1"/>
     </row>
-    <row r="89" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B89" s="1"/>
     </row>
-    <row r="90" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B90" s="1"/>
     </row>
-    <row r="91" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B91" s="1"/>
     </row>
-    <row r="92" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B92" s="1"/>
     </row>
-    <row r="93" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B93" s="1"/>
     </row>
-    <row r="94" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B94" s="1"/>
     </row>
-    <row r="95" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B95" s="1"/>
     </row>
-    <row r="96" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B96" s="1"/>
     </row>
-    <row r="97" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B97" s="1"/>
     </row>
-    <row r="98" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B98" s="1"/>
     </row>
-    <row r="99" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B99" s="1"/>
     </row>
-    <row r="100" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="2:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B100" s="1"/>
     </row>
   </sheetData>
